--- a/令和9年度_授業数カウント.xlsx
+++ b/令和9年度_授業数カウント.xlsx
@@ -17978,8 +17978,16 @@
           <t>月６</t>
         </is>
       </c>
-      <c r="H235" s="159" t="n"/>
-      <c r="I235" s="180" t="n"/>
+      <c r="H235" s="159" t="inlineStr">
+        <is>
+          <t>未来マップ</t>
+        </is>
+      </c>
+      <c r="I235" s="180" t="inlineStr">
+        <is>
+          <t>未来マップ</t>
+        </is>
+      </c>
       <c r="J235" s="158" t="inlineStr">
         <is>
           <t>金１</t>
@@ -19594,8 +19602,16 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="H259" s="159" t="n"/>
-      <c r="I259" s="180" t="n"/>
+      <c r="H259" s="159" t="inlineStr">
+        <is>
+          <t>未来マップ</t>
+        </is>
+      </c>
+      <c r="I259" s="180" t="inlineStr">
+        <is>
+          <t>未来マップ</t>
+        </is>
+      </c>
       <c r="J259" s="158" t="inlineStr">
         <is>
           <t>月１</t>

--- a/令和9年度_授業数カウント.xlsx
+++ b/令和9年度_授業数カウント.xlsx
@@ -235,12 +235,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009BC2E6"/>
+        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
+        <fgColor rgb="009BC2E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -1230,7 +1230,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="405">
+  <cellXfs count="406">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2272,16 +2272,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2293,17 +2299,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2311,7 +2314,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2326,10 +2329,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2344,22 +2347,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2380,31 +2380,32 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2413,10 +2414,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2544,7 +2545,7 @@
         <t>2年は総合のかわりに学活</t>
       </text>
     </comment>
-    <comment ref="O168" authorId="0" shapeId="0">
+    <comment ref="O169" authorId="0" shapeId="0">
       <text>
         <t>2年は総合のかわりに道徳</t>
       </text>
@@ -2564,12 +2565,12 @@
         <t>2年は総合のかわりに学活</t>
       </text>
     </comment>
-    <comment ref="O261" authorId="0" shapeId="0">
+    <comment ref="O263" authorId="0" shapeId="0">
       <text>
         <t>2年は総合のかわりに道徳</t>
       </text>
     </comment>
-    <comment ref="O298" authorId="0" shapeId="0">
+    <comment ref="O301" authorId="0" shapeId="0">
       <text>
         <t>2年は総合のかわりに学活</t>
       </text>
@@ -4525,9 +4526,9 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="H22" s="159" t="inlineStr">
-        <is>
-          <t>火５</t>
+      <c r="H22" s="349" t="inlineStr">
+        <is>
+          <t>木３</t>
         </is>
       </c>
       <c r="I22" s="180" t="inlineStr">
@@ -4555,12 +4556,12 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="N22" s="159" t="inlineStr">
-        <is>
-          <t>火５</t>
-        </is>
-      </c>
-      <c r="O22" s="349" t="inlineStr">
+      <c r="N22" s="349" t="inlineStr">
+        <is>
+          <t>木３</t>
+        </is>
+      </c>
+      <c r="O22" s="350" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -4585,9 +4586,9 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="T22" s="159" t="inlineStr">
-        <is>
-          <t>火５</t>
+      <c r="T22" s="349" t="inlineStr">
+        <is>
+          <t>木３</t>
         </is>
       </c>
       <c r="U22" s="77" t="inlineStr">
@@ -4717,9 +4718,9 @@
           <t>木２</t>
         </is>
       </c>
-      <c r="F24" s="159" t="inlineStr">
-        <is>
-          <t>木３</t>
+      <c r="F24" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="G24" s="159" t="inlineStr">
@@ -4743,9 +4744,9 @@
           <t>木２</t>
         </is>
       </c>
-      <c r="L24" s="159" t="inlineStr">
-        <is>
-          <t>木３</t>
+      <c r="L24" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="M24" s="159" t="inlineStr">
@@ -4769,9 +4770,9 @@
           <t>木２</t>
         </is>
       </c>
-      <c r="R24" s="159" t="inlineStr">
-        <is>
-          <t>木３</t>
+      <c r="R24" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="S24" s="159" t="inlineStr">
@@ -4820,9 +4821,9 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="H25" s="180" t="inlineStr">
-        <is>
-          <t>金５</t>
+      <c r="H25" s="351" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="I25" s="277" t="inlineStr">
@@ -4850,9 +4851,9 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="N25" s="77" t="inlineStr">
-        <is>
-          <t>金５</t>
+      <c r="N25" s="352" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="O25" s="225" t="inlineStr">
@@ -4880,9 +4881,9 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="T25" s="180" t="inlineStr">
-        <is>
-          <t>金５</t>
+      <c r="T25" s="351" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="U25" s="225" t="inlineStr">
@@ -5160,12 +5161,12 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="G30" s="350" t="inlineStr">
+      <c r="G30" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="H30" s="350" t="inlineStr">
+      <c r="H30" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -5190,12 +5191,12 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="M30" s="350" t="inlineStr">
+      <c r="M30" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="N30" s="350" t="inlineStr">
+      <c r="N30" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -5220,12 +5221,12 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="S30" s="350" t="inlineStr">
+      <c r="S30" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="T30" s="350" t="inlineStr">
+      <c r="T30" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -5283,92 +5284,92 @@
           <t>⑤⑥進路説明会(3年)・部活保護者会</t>
         </is>
       </c>
-      <c r="D32" s="351" t="inlineStr">
+      <c r="D32" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="E32" s="352" t="inlineStr">
+      <c r="E32" s="354" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F32" s="352" t="inlineStr">
+      <c r="F32" s="354" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="G32" s="353" t="inlineStr">
+      <c r="G32" s="355" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="H32" s="353" t="inlineStr">
+      <c r="H32" s="355" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="I32" s="354" t="inlineStr">
+      <c r="I32" s="356" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="J32" s="351" t="inlineStr">
+      <c r="J32" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="K32" s="352" t="inlineStr">
+      <c r="K32" s="354" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L32" s="352" t="inlineStr">
+      <c r="L32" s="354" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="M32" s="353" t="inlineStr">
+      <c r="M32" s="355" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="N32" s="353" t="inlineStr">
+      <c r="N32" s="355" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="O32" s="355" t="inlineStr">
+      <c r="O32" s="357" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="P32" s="351" t="inlineStr">
+      <c r="P32" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="Q32" s="352" t="inlineStr">
+      <c r="Q32" s="354" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R32" s="352" t="inlineStr">
+      <c r="R32" s="354" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="S32" s="353" t="inlineStr">
+      <c r="S32" s="355" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="T32" s="353" t="inlineStr">
+      <c r="T32" s="355" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="U32" s="355" t="inlineStr">
+      <c r="U32" s="357" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -5545,17 +5546,17 @@
           <t>本時間割</t>
         </is>
       </c>
-      <c r="D38" s="356" t="inlineStr">
+      <c r="D38" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E38" s="350" t="inlineStr">
+      <c r="E38" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F38" s="350" t="inlineStr">
+      <c r="F38" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -5571,17 +5572,17 @@
         </is>
       </c>
       <c r="I38" s="180" t="n"/>
-      <c r="J38" s="356" t="inlineStr">
+      <c r="J38" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="K38" s="350" t="inlineStr">
+      <c r="K38" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L38" s="350" t="inlineStr">
+      <c r="L38" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -5597,17 +5598,17 @@
         </is>
       </c>
       <c r="O38" s="77" t="n"/>
-      <c r="P38" s="356" t="inlineStr">
+      <c r="P38" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="Q38" s="350" t="inlineStr">
+      <c r="Q38" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="R38" s="350" t="inlineStr">
+      <c r="R38" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -5643,9 +5644,9 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="E39" s="159" t="inlineStr">
-        <is>
-          <t>金２</t>
+      <c r="E39" s="349" t="inlineStr">
+        <is>
+          <t>金５</t>
         </is>
       </c>
       <c r="F39" s="159" t="inlineStr">
@@ -5653,12 +5654,12 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="G39" s="350" t="inlineStr">
+      <c r="G39" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H39" s="350" t="inlineStr">
+      <c r="H39" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -5673,9 +5674,9 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="K39" s="159" t="inlineStr">
-        <is>
-          <t>金２</t>
+      <c r="K39" s="349" t="inlineStr">
+        <is>
+          <t>金５</t>
         </is>
       </c>
       <c r="L39" s="159" t="inlineStr">
@@ -5683,12 +5684,12 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="M39" s="350" t="inlineStr">
+      <c r="M39" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="N39" s="350" t="inlineStr">
+      <c r="N39" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -5703,9 +5704,9 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="Q39" s="159" t="inlineStr">
-        <is>
-          <t>金２</t>
+      <c r="Q39" s="349" t="inlineStr">
+        <is>
+          <t>金５</t>
         </is>
       </c>
       <c r="R39" s="159" t="inlineStr">
@@ -5713,7 +5714,7 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="S39" s="350" t="inlineStr">
+      <c r="S39" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
@@ -5872,7 +5873,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="O43" s="349" t="inlineStr">
+      <c r="O43" s="350" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -5947,7 +5948,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="I44" s="357" t="inlineStr">
+      <c r="I44" s="351" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -5977,7 +5978,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="O44" s="358" t="inlineStr">
+      <c r="O44" s="352" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -6007,7 +6008,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="U44" s="358" t="inlineStr">
+      <c r="U44" s="352" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -6038,14 +6039,14 @@
           <t>木３</t>
         </is>
       </c>
-      <c r="G45" s="159" t="inlineStr">
-        <is>
-          <t>木４</t>
-        </is>
-      </c>
-      <c r="H45" s="350" t="inlineStr">
+      <c r="G45" s="349" t="inlineStr">
         <is>
           <t>月５</t>
+        </is>
+      </c>
+      <c r="H45" s="159" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="I45" s="180" t="n"/>
@@ -6064,14 +6065,14 @@
           <t>木３</t>
         </is>
       </c>
-      <c r="M45" s="159" t="inlineStr">
-        <is>
-          <t>木４</t>
-        </is>
-      </c>
-      <c r="N45" s="350" t="inlineStr">
+      <c r="M45" s="349" t="inlineStr">
         <is>
           <t>月５</t>
+        </is>
+      </c>
+      <c r="N45" s="159" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="O45" s="77" t="n"/>
@@ -6090,14 +6091,14 @@
           <t>木３</t>
         </is>
       </c>
-      <c r="S45" s="159" t="inlineStr">
-        <is>
-          <t>木４</t>
-        </is>
-      </c>
-      <c r="T45" s="350" t="inlineStr">
+      <c r="S45" s="349" t="inlineStr">
         <is>
           <t>月５</t>
+        </is>
+      </c>
+      <c r="T45" s="159" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="U45" s="77" t="n"/>
@@ -6443,9 +6444,9 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="F51" s="159" t="inlineStr">
-        <is>
-          <t>水３</t>
+      <c r="F51" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="G51" s="159" t="inlineStr">
@@ -6465,9 +6466,9 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="L51" s="159" t="inlineStr">
-        <is>
-          <t>水３</t>
+      <c r="L51" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="M51" s="159" t="inlineStr">
@@ -6487,9 +6488,9 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="R51" s="159" t="inlineStr">
-        <is>
-          <t>水３</t>
+      <c r="R51" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="S51" s="159" t="inlineStr">
@@ -6791,7 +6792,7 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="H56" s="350" t="inlineStr">
+      <c r="H56" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
@@ -6821,7 +6822,7 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="N56" s="350" t="inlineStr">
+      <c r="N56" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
@@ -6851,7 +6852,7 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="T56" s="350" t="inlineStr">
+      <c r="T56" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
@@ -6882,9 +6883,9 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="F57" s="159" t="inlineStr">
-        <is>
-          <t>火３</t>
+      <c r="F57" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
         </is>
       </c>
       <c r="G57" s="159" t="inlineStr">
@@ -6912,9 +6913,9 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="L57" s="159" t="inlineStr">
-        <is>
-          <t>火３</t>
+      <c r="L57" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
         </is>
       </c>
       <c r="M57" s="159" t="inlineStr">
@@ -6942,9 +6943,9 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="R57" s="159" t="inlineStr">
-        <is>
-          <t>火３</t>
+      <c r="R57" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
         </is>
       </c>
       <c r="S57" s="159" t="inlineStr">
@@ -6988,9 +6989,9 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="G58" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
+      <c r="G58" s="349" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="H58" s="159" t="inlineStr">
@@ -7018,9 +7019,9 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="M58" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
+      <c r="M58" s="349" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="N58" s="159" t="inlineStr">
@@ -7048,9 +7049,9 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="S58" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
+      <c r="S58" s="349" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="T58" s="159" t="inlineStr">
@@ -7083,9 +7084,9 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="E59" s="159" t="inlineStr">
-        <is>
-          <t>木２</t>
+      <c r="E59" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
         </is>
       </c>
       <c r="F59" s="159" t="inlineStr">
@@ -7109,9 +7110,9 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="K59" s="191" t="inlineStr">
-        <is>
-          <t>木２</t>
+      <c r="K59" s="360" t="inlineStr">
+        <is>
+          <t>月５</t>
         </is>
       </c>
       <c r="L59" s="191" t="inlineStr">
@@ -7135,9 +7136,9 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="Q59" s="159" t="inlineStr">
-        <is>
-          <t>木２</t>
+      <c r="Q59" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
         </is>
       </c>
       <c r="R59" s="159" t="inlineStr">
@@ -7334,72 +7335,72 @@
           <t>教育相談（全学年）</t>
         </is>
       </c>
-      <c r="D63" s="360" t="inlineStr">
+      <c r="D63" s="361" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E63" s="361" t="inlineStr">
+      <c r="E63" s="362" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F63" s="362" t="inlineStr">
+      <c r="F63" s="363" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="G63" s="361" t="inlineStr">
+      <c r="G63" s="362" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H63" s="361" t="n"/>
-      <c r="I63" s="363" t="n"/>
-      <c r="J63" s="360" t="inlineStr">
+      <c r="H63" s="362" t="n"/>
+      <c r="I63" s="364" t="n"/>
+      <c r="J63" s="361" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="K63" s="361" t="inlineStr">
+      <c r="K63" s="362" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L63" s="362" t="inlineStr">
+      <c r="L63" s="363" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="M63" s="361" t="inlineStr">
+      <c r="M63" s="362" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="N63" s="361" t="n"/>
-      <c r="O63" s="364" t="n"/>
-      <c r="P63" s="360" t="inlineStr">
+      <c r="N63" s="362" t="n"/>
+      <c r="O63" s="365" t="n"/>
+      <c r="P63" s="361" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="Q63" s="361" t="inlineStr">
+      <c r="Q63" s="362" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="R63" s="362" t="inlineStr">
+      <c r="R63" s="363" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="S63" s="361" t="inlineStr">
+      <c r="S63" s="362" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="T63" s="361" t="n"/>
-      <c r="U63" s="364" t="n"/>
+      <c r="T63" s="362" t="n"/>
+      <c r="U63" s="365" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="187" t="n">
@@ -7420,66 +7421,66 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="E64" s="365" t="inlineStr">
+      <c r="E64" s="366" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="F64" s="365" t="inlineStr">
+      <c r="F64" s="366" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="G64" s="365" t="inlineStr">
+      <c r="G64" s="366" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="H64" s="366" t="n"/>
+      <c r="H64" s="367" t="n"/>
       <c r="I64" s="342" t="n"/>
       <c r="J64" s="239" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="K64" s="365" t="inlineStr">
+      <c r="K64" s="366" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="L64" s="365" t="inlineStr">
+      <c r="L64" s="366" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="M64" s="365" t="inlineStr">
+      <c r="M64" s="366" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="N64" s="366" t="n"/>
+      <c r="N64" s="367" t="n"/>
       <c r="O64" s="343" t="n"/>
       <c r="P64" s="239" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="Q64" s="365" t="inlineStr">
+      <c r="Q64" s="366" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="R64" s="365" t="inlineStr">
+      <c r="R64" s="366" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S64" s="365" t="inlineStr">
+      <c r="S64" s="366" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="T64" s="366" t="n"/>
+      <c r="T64" s="367" t="n"/>
       <c r="U64" s="343" t="n"/>
     </row>
     <row r="65">
@@ -7655,7 +7656,7 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="H67" s="367" t="inlineStr">
+      <c r="H67" s="368" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -7685,12 +7686,12 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="N67" s="367" t="inlineStr">
+      <c r="N67" s="368" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
       </c>
-      <c r="O67" s="349" t="inlineStr">
+      <c r="O67" s="350" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -7715,7 +7716,7 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="T67" s="367" t="inlineStr">
+      <c r="T67" s="368" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -7813,7 +7814,7 @@
           <t>月３</t>
         </is>
       </c>
-      <c r="G70" s="350" t="inlineStr">
+      <c r="G70" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -7843,7 +7844,7 @@
           <t>月３</t>
         </is>
       </c>
-      <c r="M70" s="368" t="inlineStr">
+      <c r="M70" s="369" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -7861,7 +7862,7 @@
       <c r="P70" s="158" t="n"/>
       <c r="Q70" s="159" t="n"/>
       <c r="R70" s="159" t="n"/>
-      <c r="S70" s="350" t="inlineStr">
+      <c r="S70" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -7901,49 +7902,49 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="F71" s="350" t="inlineStr">
+      <c r="F71" s="159" t="inlineStr">
+        <is>
+          <t>火３</t>
+        </is>
+      </c>
+      <c r="G71" s="159" t="inlineStr">
+        <is>
+          <t>火４</t>
+        </is>
+      </c>
+      <c r="H71" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G71" s="159" t="inlineStr">
+      <c r="I71" s="180" t="inlineStr">
+        <is>
+          <t>火６</t>
+        </is>
+      </c>
+      <c r="J71" s="158" t="inlineStr">
+        <is>
+          <t>火１</t>
+        </is>
+      </c>
+      <c r="K71" s="159" t="inlineStr">
+        <is>
+          <t>火２</t>
+        </is>
+      </c>
+      <c r="L71" s="159" t="inlineStr">
+        <is>
+          <t>火３</t>
+        </is>
+      </c>
+      <c r="M71" s="159" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="H71" s="159" t="inlineStr">
-        <is>
-          <t>火５</t>
-        </is>
-      </c>
-      <c r="I71" s="180" t="inlineStr">
-        <is>
-          <t>火６</t>
-        </is>
-      </c>
-      <c r="J71" s="158" t="inlineStr">
-        <is>
-          <t>火１</t>
-        </is>
-      </c>
-      <c r="K71" s="159" t="inlineStr">
-        <is>
-          <t>火２</t>
-        </is>
-      </c>
-      <c r="L71" s="350" t="inlineStr">
+      <c r="N71" s="349" t="inlineStr">
         <is>
           <t>水３</t>
-        </is>
-      </c>
-      <c r="M71" s="159" t="inlineStr">
-        <is>
-          <t>火４</t>
-        </is>
-      </c>
-      <c r="N71" s="159" t="inlineStr">
-        <is>
-          <t>火５</t>
         </is>
       </c>
       <c r="O71" s="77" t="inlineStr">
@@ -7982,9 +7983,9 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="F72" s="350" t="inlineStr">
-        <is>
-          <t>月３</t>
+      <c r="F72" s="349" t="inlineStr">
+        <is>
+          <t>木４</t>
         </is>
       </c>
       <c r="G72" s="159" t="inlineStr">
@@ -8012,9 +8013,9 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="L72" s="350" t="inlineStr">
-        <is>
-          <t>月３</t>
+      <c r="L72" s="349" t="inlineStr">
+        <is>
+          <t>木４</t>
         </is>
       </c>
       <c r="M72" s="159" t="inlineStr">
@@ -8219,12 +8220,12 @@
       <c r="M75" s="159" t="n"/>
       <c r="N75" s="159" t="n"/>
       <c r="O75" s="77" t="n"/>
-      <c r="P75" s="369" t="n"/>
-      <c r="Q75" s="370" t="n"/>
-      <c r="R75" s="371" t="n"/>
+      <c r="P75" s="370" t="n"/>
+      <c r="Q75" s="371" t="n"/>
+      <c r="R75" s="372" t="n"/>
       <c r="S75" s="156" t="n"/>
       <c r="T75" s="156" t="n"/>
-      <c r="U75" s="372" t="n"/>
+      <c r="U75" s="373" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="45" t="n">
@@ -8289,12 +8290,12 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="H77" s="350" t="inlineStr">
+      <c r="H77" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="I77" s="357" t="inlineStr">
+      <c r="I77" s="351" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -8319,12 +8320,12 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="N77" s="350" t="inlineStr">
+      <c r="N77" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="O77" s="358" t="inlineStr">
+      <c r="O77" s="352" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -8349,12 +8350,12 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="T77" s="350" t="inlineStr">
+      <c r="T77" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="U77" s="358" t="inlineStr">
+      <c r="U77" s="352" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -8389,12 +8390,12 @@
           <t>火３</t>
         </is>
       </c>
-      <c r="G78" s="350" t="inlineStr">
+      <c r="G78" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="H78" s="350" t="inlineStr">
+      <c r="H78" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -8419,12 +8420,12 @@
           <t>火３</t>
         </is>
       </c>
-      <c r="M78" s="350" t="inlineStr">
+      <c r="M78" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="N78" s="350" t="inlineStr">
+      <c r="N78" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -8434,27 +8435,27 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="P78" s="369" t="inlineStr">
+      <c r="P78" s="370" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="Q78" s="370" t="inlineStr">
+      <c r="Q78" s="371" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="R78" s="370" t="inlineStr">
+      <c r="R78" s="371" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S78" s="373" t="inlineStr">
+      <c r="S78" s="360" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="T78" s="373" t="inlineStr">
+      <c r="T78" s="360" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -8539,17 +8540,17 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="P79" s="369" t="inlineStr">
+      <c r="P79" s="370" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="Q79" s="370" t="inlineStr">
+      <c r="Q79" s="371" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="R79" s="370" t="inlineStr">
+      <c r="R79" s="371" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
@@ -8636,17 +8637,17 @@
         </is>
       </c>
       <c r="O80" s="77" t="n"/>
-      <c r="P80" s="369" t="inlineStr">
+      <c r="P80" s="370" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="Q80" s="370" t="inlineStr">
+      <c r="Q80" s="371" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R80" s="370" t="inlineStr">
+      <c r="R80" s="371" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -8855,12 +8856,12 @@
           <t>月３</t>
         </is>
       </c>
-      <c r="G84" s="350" t="inlineStr">
+      <c r="G84" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="H84" s="350" t="inlineStr">
+      <c r="H84" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -8885,12 +8886,12 @@
           <t>月３</t>
         </is>
       </c>
-      <c r="M84" s="350" t="inlineStr">
+      <c r="M84" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="N84" s="350" t="inlineStr">
+      <c r="N84" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -8915,12 +8916,12 @@
           <t>月３</t>
         </is>
       </c>
-      <c r="S84" s="350" t="inlineStr">
+      <c r="S84" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="T84" s="350" t="inlineStr">
+      <c r="T84" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -8960,12 +8961,12 @@
           <t>火３</t>
         </is>
       </c>
-      <c r="G85" s="350" t="inlineStr">
+      <c r="G85" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H85" s="350" t="inlineStr">
+      <c r="H85" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -8990,12 +8991,12 @@
           <t>火３</t>
         </is>
       </c>
-      <c r="M85" s="350" t="inlineStr">
+      <c r="M85" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="N85" s="350" t="inlineStr">
+      <c r="N85" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -9020,12 +9021,12 @@
           <t>火３</t>
         </is>
       </c>
-      <c r="S85" s="350" t="inlineStr">
+      <c r="S85" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="T85" s="350" t="inlineStr">
+      <c r="T85" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -9409,92 +9410,92 @@
           <t>腎臓検診②</t>
         </is>
       </c>
-      <c r="D93" s="360" t="inlineStr">
+      <c r="D93" s="361" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="E93" s="361" t="inlineStr">
-        <is>
-          <t>水２</t>
-        </is>
-      </c>
-      <c r="F93" s="361" t="inlineStr">
+      <c r="E93" s="363" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="F93" s="362" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G93" s="361" t="inlineStr">
+      <c r="G93" s="362" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="H93" s="361" t="inlineStr">
+      <c r="H93" s="362" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
       </c>
-      <c r="I93" s="363" t="inlineStr">
+      <c r="I93" s="364" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
       </c>
-      <c r="J93" s="360" t="inlineStr">
+      <c r="J93" s="361" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="K93" s="361" t="inlineStr">
-        <is>
-          <t>水２</t>
-        </is>
-      </c>
-      <c r="L93" s="361" t="inlineStr">
+      <c r="K93" s="363" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="L93" s="362" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="M93" s="361" t="inlineStr">
+      <c r="M93" s="362" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="N93" s="361" t="inlineStr">
+      <c r="N93" s="362" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
       </c>
-      <c r="O93" s="364" t="inlineStr">
+      <c r="O93" s="365" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
       </c>
-      <c r="P93" s="360" t="inlineStr">
+      <c r="P93" s="361" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="Q93" s="361" t="inlineStr">
-        <is>
-          <t>水２</t>
-        </is>
-      </c>
-      <c r="R93" s="361" t="inlineStr">
+      <c r="Q93" s="363" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="R93" s="362" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="S93" s="361" t="inlineStr">
+      <c r="S93" s="362" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="T93" s="361" t="inlineStr">
+      <c r="T93" s="362" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
       </c>
-      <c r="U93" s="364" t="inlineStr">
+      <c r="U93" s="365" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -9847,7 +9848,7 @@
           <t>保護者会（全）・第１回いじめ防対会議</t>
         </is>
       </c>
-      <c r="D99" s="356" t="inlineStr">
+      <c r="D99" s="358" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -9869,7 +9870,7 @@
       </c>
       <c r="H99" s="194" t="n"/>
       <c r="I99" s="180" t="n"/>
-      <c r="J99" s="356" t="inlineStr">
+      <c r="J99" s="358" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -9891,7 +9892,7 @@
       </c>
       <c r="N99" s="194" t="n"/>
       <c r="O99" s="77" t="n"/>
-      <c r="P99" s="356" t="inlineStr">
+      <c r="P99" s="358" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -10009,7 +10010,7 @@
           <t>保護者会（全）</t>
         </is>
       </c>
-      <c r="D101" s="356" t="inlineStr">
+      <c r="D101" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -10031,7 +10032,7 @@
       </c>
       <c r="H101" s="194" t="n"/>
       <c r="I101" s="180" t="n"/>
-      <c r="J101" s="356" t="inlineStr">
+      <c r="J101" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -10053,7 +10054,7 @@
       </c>
       <c r="N101" s="194" t="n"/>
       <c r="O101" s="77" t="n"/>
-      <c r="P101" s="356" t="inlineStr">
+      <c r="P101" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -10106,7 +10107,7 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="H102" s="367" t="inlineStr">
+      <c r="H102" s="368" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -10136,7 +10137,7 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="N102" s="367" t="inlineStr">
+      <c r="N102" s="368" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -10166,7 +10167,7 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="T102" s="367" t="inlineStr">
+      <c r="T102" s="368" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -10365,7 +10366,7 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="E106" s="368" t="inlineStr">
+      <c r="E106" s="369" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -10395,7 +10396,7 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="K106" s="368" t="inlineStr">
+      <c r="K106" s="369" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -10415,7 +10416,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="O106" s="349" t="inlineStr">
+      <c r="O106" s="350" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -10425,7 +10426,7 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="Q106" s="368" t="inlineStr">
+      <c r="Q106" s="369" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -10471,7 +10472,7 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="F107" s="350" t="inlineStr">
+      <c r="F107" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -10501,7 +10502,7 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="L107" s="350" t="inlineStr">
+      <c r="L107" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -10531,7 +10532,7 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="R107" s="350" t="inlineStr">
+      <c r="R107" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -10827,7 +10828,7 @@
         </is>
       </c>
       <c r="D113" s="158" t="n"/>
-      <c r="E113" s="350" t="inlineStr">
+      <c r="E113" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -10837,7 +10838,7 @@
       <c r="H113" s="159" t="n"/>
       <c r="I113" s="180" t="n"/>
       <c r="J113" s="158" t="n"/>
-      <c r="K113" s="350" t="inlineStr">
+      <c r="K113" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -10847,7 +10848,7 @@
       <c r="N113" s="159" t="n"/>
       <c r="O113" s="77" t="n"/>
       <c r="P113" s="158" t="n"/>
-      <c r="Q113" s="350" t="inlineStr">
+      <c r="Q113" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -12092,24 +12093,24 @@
         </is>
       </c>
       <c r="C155" s="41" t="n"/>
-      <c r="D155" s="360" t="n"/>
-      <c r="E155" s="361" t="n"/>
-      <c r="F155" s="361" t="n"/>
-      <c r="G155" s="361" t="n"/>
-      <c r="H155" s="361" t="n"/>
-      <c r="I155" s="363" t="n"/>
-      <c r="J155" s="360" t="n"/>
-      <c r="K155" s="361" t="n"/>
-      <c r="L155" s="361" t="n"/>
-      <c r="M155" s="361" t="n"/>
-      <c r="N155" s="361" t="n"/>
-      <c r="O155" s="364" t="n"/>
-      <c r="P155" s="360" t="n"/>
-      <c r="Q155" s="361" t="n"/>
-      <c r="R155" s="361" t="n"/>
-      <c r="S155" s="361" t="n"/>
-      <c r="T155" s="361" t="n"/>
-      <c r="U155" s="364" t="n"/>
+      <c r="D155" s="361" t="n"/>
+      <c r="E155" s="362" t="n"/>
+      <c r="F155" s="362" t="n"/>
+      <c r="G155" s="362" t="n"/>
+      <c r="H155" s="362" t="n"/>
+      <c r="I155" s="364" t="n"/>
+      <c r="J155" s="361" t="n"/>
+      <c r="K155" s="362" t="n"/>
+      <c r="L155" s="362" t="n"/>
+      <c r="M155" s="362" t="n"/>
+      <c r="N155" s="362" t="n"/>
+      <c r="O155" s="365" t="n"/>
+      <c r="P155" s="361" t="n"/>
+      <c r="Q155" s="362" t="n"/>
+      <c r="R155" s="362" t="n"/>
+      <c r="S155" s="362" t="n"/>
+      <c r="T155" s="362" t="n"/>
+      <c r="U155" s="365" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1" s="337" thickBot="1">
       <c r="A156" s="187" t="n">
@@ -12166,17 +12167,17 @@
         </is>
       </c>
       <c r="C157" s="41" t="n"/>
-      <c r="D157" s="356" t="inlineStr">
+      <c r="D157" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E157" s="350" t="inlineStr">
+      <c r="E157" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="F157" s="357" t="inlineStr">
+      <c r="F157" s="351" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -12192,17 +12193,17 @@
         </is>
       </c>
       <c r="I157" s="180" t="n"/>
-      <c r="J157" s="356" t="inlineStr">
+      <c r="J157" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="K157" s="350" t="inlineStr">
+      <c r="K157" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="L157" s="357" t="inlineStr">
+      <c r="L157" s="351" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -12218,17 +12219,17 @@
         </is>
       </c>
       <c r="O157" s="77" t="n"/>
-      <c r="P157" s="356" t="inlineStr">
+      <c r="P157" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="Q157" s="350" t="inlineStr">
+      <c r="Q157" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="R157" s="357" t="inlineStr">
+      <c r="R157" s="351" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -12255,17 +12256,17 @@
         </is>
       </c>
       <c r="C158" s="41" t="n"/>
-      <c r="D158" s="351" t="inlineStr">
+      <c r="D158" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="E158" s="350" t="inlineStr">
+      <c r="E158" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F158" s="350" t="inlineStr">
+      <c r="F158" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -12275,7 +12276,7 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="H158" s="352" t="inlineStr">
+      <c r="H158" s="354" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -12285,17 +12286,17 @@
           <t>金６</t>
         </is>
       </c>
-      <c r="J158" s="351" t="inlineStr">
+      <c r="J158" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="K158" s="350" t="inlineStr">
+      <c r="K158" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L158" s="350" t="inlineStr">
+      <c r="L158" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -12305,7 +12306,7 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="N158" s="350" t="inlineStr">
+      <c r="N158" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -12315,17 +12316,17 @@
           <t>金６</t>
         </is>
       </c>
-      <c r="P158" s="351" t="inlineStr">
+      <c r="P158" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="Q158" s="350" t="inlineStr">
+      <c r="Q158" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R158" s="367" t="inlineStr">
+      <c r="R158" s="368" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -12335,7 +12336,7 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="T158" s="350" t="inlineStr">
+      <c r="T158" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -12439,7 +12440,7 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="I161" s="357" t="inlineStr">
+      <c r="I161" s="351" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -12469,7 +12470,7 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="O161" s="358" t="inlineStr">
+      <c r="O161" s="352" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -12499,7 +12500,7 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="U161" s="358" t="inlineStr">
+      <c r="U161" s="352" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -12624,7 +12625,7 @@
           <t>選挙管理委員会・私立合同説明会</t>
         </is>
       </c>
-      <c r="D163" s="356" t="inlineStr">
+      <c r="D163" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -12654,7 +12655,7 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="J163" s="356" t="inlineStr">
+      <c r="J163" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -12684,7 +12685,7 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="P163" s="356" t="inlineStr">
+      <c r="P163" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -12837,7 +12838,7 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="G165" s="350" t="inlineStr">
+      <c r="G165" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -12867,7 +12868,7 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="M165" s="350" t="inlineStr">
+      <c r="M165" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -12897,7 +12898,7 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="S165" s="350" t="inlineStr">
+      <c r="S165" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -13186,9 +13187,9 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="I168" s="357" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="I168" s="351" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="J168" s="158" t="inlineStr">
@@ -13216,9 +13217,9 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="O168" s="349" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="O168" s="352" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="P168" s="158" t="inlineStr">
@@ -13246,9 +13247,9 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="U168" s="358" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="U168" s="352" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="X168" s="44" t="inlineStr">
@@ -13377,9 +13378,9 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="I169" s="357" t="inlineStr">
-        <is>
-          <t>水６</t>
+      <c r="I169" s="180" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="J169" s="158" t="inlineStr">
@@ -13407,9 +13408,9 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="O169" s="358" t="inlineStr">
-        <is>
-          <t>水６</t>
+      <c r="O169" s="350" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="P169" s="158" t="inlineStr">
@@ -13437,9 +13438,9 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="U169" s="358" t="inlineStr">
-        <is>
-          <t>水６</t>
+      <c r="U169" s="77" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="X169" s="44" t="inlineStr">
@@ -13560,7 +13561,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="I170" s="357" t="inlineStr">
+      <c r="I170" s="351" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -13590,7 +13591,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="O170" s="358" t="inlineStr">
+      <c r="O170" s="352" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -13620,7 +13621,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="U170" s="358" t="inlineStr">
+      <c r="U170" s="352" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -13807,7 +13808,7 @@
         </is>
       </c>
       <c r="C172" s="41" t="n"/>
-      <c r="D172" s="356" t="inlineStr">
+      <c r="D172" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
@@ -13837,7 +13838,7 @@
           <t>金６</t>
         </is>
       </c>
-      <c r="J172" s="356" t="inlineStr">
+      <c r="J172" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
@@ -13867,7 +13868,7 @@
           <t>金６</t>
         </is>
       </c>
-      <c r="P172" s="356" t="inlineStr">
+      <c r="P172" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
@@ -14261,21 +14262,21 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="G179" s="350" t="inlineStr">
+      <c r="G179" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H179" s="350" t="inlineStr">
+      <c r="H179" s="159" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="I179" s="351" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
-      <c r="I179" s="357" t="inlineStr">
-        <is>
-          <t>月６</t>
-        </is>
-      </c>
       <c r="J179" s="158" t="inlineStr">
         <is>
           <t>金１</t>
@@ -14291,21 +14292,21 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="M179" s="350" t="inlineStr">
+      <c r="M179" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="N179" s="350" t="inlineStr">
+      <c r="N179" s="159" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="O179" s="352" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
-      <c r="O179" s="358" t="inlineStr">
-        <is>
-          <t>月６</t>
-        </is>
-      </c>
       <c r="P179" s="158" t="inlineStr">
         <is>
           <t>金１</t>
@@ -14321,19 +14322,19 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="S179" s="350" t="inlineStr">
+      <c r="S179" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="T179" s="350" t="inlineStr">
+      <c r="T179" s="159" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="U179" s="352" t="inlineStr">
         <is>
           <t>月５</t>
-        </is>
-      </c>
-      <c r="U179" s="358" t="inlineStr">
-        <is>
-          <t>月６</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14896,7 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="F190" s="350" t="inlineStr">
+      <c r="F190" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -14925,7 +14926,7 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="L190" s="350" t="inlineStr">
+      <c r="L190" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -14955,7 +14956,7 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="R190" s="350" t="inlineStr">
+      <c r="R190" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -14990,12 +14991,12 @@
           <t>体育大会準備</t>
         </is>
       </c>
-      <c r="D191" s="356" t="inlineStr">
+      <c r="D191" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="E191" s="350" t="inlineStr">
+      <c r="E191" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -15005,19 +15006,19 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="G191" s="350" t="inlineStr">
+      <c r="G191" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
       <c r="H191" s="159" t="n"/>
       <c r="I191" s="180" t="n"/>
-      <c r="J191" s="356" t="inlineStr">
+      <c r="J191" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="K191" s="350" t="inlineStr">
+      <c r="K191" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -15027,19 +15028,19 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="M191" s="350" t="inlineStr">
+      <c r="M191" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
       <c r="N191" s="159" t="n"/>
       <c r="O191" s="180" t="n"/>
-      <c r="P191" s="356" t="inlineStr">
+      <c r="P191" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="Q191" s="350" t="inlineStr">
+      <c r="Q191" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -15049,7 +15050,7 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="S191" s="350" t="inlineStr">
+      <c r="S191" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
@@ -15114,9 +15115,9 @@
           <t>金２</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>金３</t>
+      <c r="F193" s="385" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -15144,9 +15145,9 @@
           <t>金２</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>金３</t>
+      <c r="L193" s="385" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15159,7 +15160,7 @@
           <t>金５</t>
         </is>
       </c>
-      <c r="O193" s="385" t="inlineStr">
+      <c r="O193" s="386" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -15174,9 +15175,9 @@
           <t>金２</t>
         </is>
       </c>
-      <c r="R193" t="inlineStr">
-        <is>
-          <t>金３</t>
+      <c r="R193" s="385" t="inlineStr">
+        <is>
+          <t>木５</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
@@ -15583,64 +15584,64 @@
           <t>▼実力テスト②(3年)</t>
         </is>
       </c>
-      <c r="D200" s="386" t="inlineStr">
+      <c r="D200" s="387" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E200" s="368" t="inlineStr">
+      <c r="E200" s="369" t="inlineStr">
+        <is>
+          <t>月６</t>
+        </is>
+      </c>
+      <c r="F200" s="349" t="inlineStr">
+        <is>
+          <t>月３</t>
+        </is>
+      </c>
+      <c r="G200" s="349" t="inlineStr">
+        <is>
+          <t>月４</t>
+        </is>
+      </c>
+      <c r="H200" s="159" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="I200" s="351" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F200" s="350" t="inlineStr">
+      <c r="J200" s="387" t="inlineStr">
+        <is>
+          <t>月１</t>
+        </is>
+      </c>
+      <c r="K200" s="369" t="inlineStr">
+        <is>
+          <t>月６</t>
+        </is>
+      </c>
+      <c r="L200" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G200" s="350" t="inlineStr">
+      <c r="M200" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H200" s="350" t="inlineStr">
-        <is>
-          <t>月５</t>
-        </is>
-      </c>
-      <c r="I200" s="357" t="inlineStr">
-        <is>
-          <t>月６</t>
-        </is>
-      </c>
-      <c r="J200" s="386" t="inlineStr">
-        <is>
-          <t>月１</t>
-        </is>
-      </c>
-      <c r="K200" s="368" t="inlineStr">
+      <c r="N200" s="159" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="O200" s="351" t="inlineStr">
         <is>
           <t>月２</t>
-        </is>
-      </c>
-      <c r="L200" s="350" t="inlineStr">
-        <is>
-          <t>月３</t>
-        </is>
-      </c>
-      <c r="M200" s="350" t="inlineStr">
-        <is>
-          <t>月４</t>
-        </is>
-      </c>
-      <c r="N200" s="350" t="inlineStr">
-        <is>
-          <t>月５</t>
-        </is>
-      </c>
-      <c r="O200" s="357" t="inlineStr">
-        <is>
-          <t>月６</t>
         </is>
       </c>
       <c r="P200" s="189" t="n"/>
@@ -15648,9 +15649,9 @@
       <c r="R200" s="159" t="n"/>
       <c r="S200" s="159" t="n"/>
       <c r="T200" s="159" t="n"/>
-      <c r="U200" s="357" t="inlineStr">
-        <is>
-          <t>月６</t>
+      <c r="U200" s="351" t="inlineStr">
+        <is>
+          <t>月２</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15676,7 @@
       <c r="L201" s="159" t="n"/>
       <c r="M201" s="159" t="n"/>
       <c r="N201" s="268" t="n"/>
-      <c r="P201" s="387" t="n"/>
+      <c r="P201" s="388" t="n"/>
       <c r="U201" s="180" t="n"/>
     </row>
     <row r="202">
@@ -15725,7 +15726,7 @@
           <t>認証式①ＷＥＢＱＵ</t>
         </is>
       </c>
-      <c r="D203" s="356" t="inlineStr">
+      <c r="D203" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
@@ -15755,7 +15756,7 @@
           <t>月６</t>
         </is>
       </c>
-      <c r="J203" s="356" t="inlineStr">
+      <c r="J203" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
@@ -15785,7 +15786,7 @@
           <t>月６</t>
         </is>
       </c>
-      <c r="P203" s="356" t="inlineStr">
+      <c r="P203" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
@@ -15826,7 +15827,7 @@
         </is>
       </c>
       <c r="C204" s="41" t="n"/>
-      <c r="D204" s="356" t="inlineStr">
+      <c r="D204" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -15856,7 +15857,7 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="J204" s="356" t="inlineStr">
+      <c r="J204" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -15886,7 +15887,7 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="P204" s="356" t="inlineStr">
+      <c r="P204" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -16136,69 +16137,69 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="G207" s="159" t="inlineStr">
+      <c r="G207" s="349" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="H207" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="H207" s="159" t="inlineStr">
+      <c r="I207" s="351" t="inlineStr">
+        <is>
+          <t>水５</t>
+        </is>
+      </c>
+      <c r="J207" s="189" t="inlineStr">
+        <is>
+          <t>金１</t>
+        </is>
+      </c>
+      <c r="K207" s="190" t="inlineStr">
+        <is>
+          <t>金２</t>
+        </is>
+      </c>
+      <c r="L207" s="159" t="inlineStr">
+        <is>
+          <t>金３</t>
+        </is>
+      </c>
+      <c r="M207" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="I207" s="357" t="inlineStr">
-        <is>
-          <t>月６</t>
-        </is>
-      </c>
-      <c r="J207" s="189" t="inlineStr">
+      <c r="N207" s="349" t="inlineStr">
+        <is>
+          <t>金４</t>
+        </is>
+      </c>
+      <c r="O207" s="352" t="inlineStr">
+        <is>
+          <t>水５</t>
+        </is>
+      </c>
+      <c r="P207" s="189" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="K207" s="190" t="inlineStr">
+      <c r="Q207" s="190" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="L207" s="159" t="inlineStr">
+      <c r="R207" s="159" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="M207" s="159" t="inlineStr">
-        <is>
-          <t>金４</t>
-        </is>
-      </c>
-      <c r="N207" s="159" t="inlineStr">
+      <c r="S207" s="349" t="inlineStr">
         <is>
           <t>金５</t>
-        </is>
-      </c>
-      <c r="O207" s="358" t="inlineStr">
-        <is>
-          <t>月６</t>
-        </is>
-      </c>
-      <c r="P207" s="189" t="inlineStr">
-        <is>
-          <t>金１</t>
-        </is>
-      </c>
-      <c r="Q207" s="190" t="inlineStr">
-        <is>
-          <t>金２</t>
-        </is>
-      </c>
-      <c r="R207" s="159" t="inlineStr">
-        <is>
-          <t>金３</t>
-        </is>
-      </c>
-      <c r="S207" s="159" t="inlineStr">
-        <is>
-          <t>金４</t>
         </is>
       </c>
       <c r="T207" s="159" t="n"/>
@@ -16272,7 +16273,7 @@
         </is>
       </c>
       <c r="C210" s="41" t="n"/>
-      <c r="D210" s="356" t="inlineStr">
+      <c r="D210" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -16298,7 +16299,7 @@
         </is>
       </c>
       <c r="I210" s="180" t="n"/>
-      <c r="J210" s="356" t="inlineStr">
+      <c r="J210" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -16324,7 +16325,7 @@
         </is>
       </c>
       <c r="O210" s="77" t="n"/>
-      <c r="P210" s="356" t="inlineStr">
+      <c r="P210" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -16365,7 +16366,7 @@
           <t>授業参観(午前)</t>
         </is>
       </c>
-      <c r="D211" s="356" t="inlineStr">
+      <c r="D211" s="358" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -16385,13 +16386,13 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="H211" s="350" t="inlineStr">
-        <is>
-          <t>金５</t>
+      <c r="H211" s="349" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="I211" s="180" t="n"/>
-      <c r="J211" s="356" t="inlineStr">
+      <c r="J211" s="358" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -16411,13 +16412,13 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="N211" s="350" t="inlineStr">
-        <is>
-          <t>金５</t>
+      <c r="N211" s="349" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="O211" s="77" t="n"/>
-      <c r="P211" s="356" t="inlineStr">
+      <c r="P211" s="358" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -16437,9 +16438,9 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="T211" s="350" t="inlineStr">
-        <is>
-          <t>金５</t>
+      <c r="T211" s="349" t="inlineStr">
+        <is>
+          <t>火６</t>
         </is>
       </c>
       <c r="U211" s="77" t="n"/>
@@ -16454,7 +16455,7 @@
         </is>
       </c>
       <c r="C212" s="41" t="n"/>
-      <c r="D212" s="356" t="inlineStr">
+      <c r="D212" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -16469,7 +16470,7 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="G212" s="350" t="inlineStr">
+      <c r="G212" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -16480,7 +16481,7 @@
         </is>
       </c>
       <c r="I212" s="180" t="n"/>
-      <c r="J212" s="356" t="inlineStr">
+      <c r="J212" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -16495,7 +16496,7 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="M212" s="350" t="inlineStr">
+      <c r="M212" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -16506,7 +16507,7 @@
         </is>
       </c>
       <c r="O212" s="77" t="n"/>
-      <c r="P212" s="356" t="inlineStr">
+      <c r="P212" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -16521,7 +16522,7 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="S212" s="350" t="inlineStr">
+      <c r="S212" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -16779,7 +16780,7 @@
         </is>
       </c>
       <c r="C217" s="41" t="n"/>
-      <c r="D217" s="356" t="inlineStr">
+      <c r="D217" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -16799,13 +16800,13 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="H217" s="350" t="inlineStr">
+      <c r="H217" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
       <c r="I217" s="180" t="n"/>
-      <c r="J217" s="356" t="inlineStr">
+      <c r="J217" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -16825,13 +16826,13 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="N217" s="350" t="inlineStr">
+      <c r="N217" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
       <c r="O217" s="77" t="n"/>
-      <c r="P217" s="356" t="inlineStr">
+      <c r="P217" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -16851,7 +16852,7 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="T217" s="350" t="inlineStr">
+      <c r="T217" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -16872,12 +16873,12 @@
           <t>文化祭(音楽発表会)準備</t>
         </is>
       </c>
-      <c r="D218" s="356" t="inlineStr">
+      <c r="D218" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="E218" s="350" t="inlineStr">
+      <c r="E218" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -16894,12 +16895,12 @@
       </c>
       <c r="H218" s="159" t="n"/>
       <c r="I218" s="180" t="n"/>
-      <c r="J218" s="356" t="inlineStr">
+      <c r="J218" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="K218" s="350" t="inlineStr">
+      <c r="K218" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -16916,12 +16917,12 @@
       </c>
       <c r="N218" s="159" t="n"/>
       <c r="O218" s="77" t="n"/>
-      <c r="P218" s="356" t="inlineStr">
+      <c r="P218" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="Q218" s="350" t="inlineStr">
+      <c r="Q218" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -16990,7 +16991,7 @@
       <c r="E220" s="159" t="n"/>
       <c r="F220" s="159" t="n"/>
       <c r="G220" s="159" t="n"/>
-      <c r="H220" s="350" t="inlineStr">
+      <c r="H220" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -17000,7 +17001,7 @@
       <c r="K220" s="159" t="n"/>
       <c r="L220" s="159" t="n"/>
       <c r="M220" s="159" t="n"/>
-      <c r="N220" s="350" t="inlineStr">
+      <c r="N220" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -17010,7 +17011,7 @@
       <c r="Q220" s="159" t="n"/>
       <c r="R220" s="159" t="n"/>
       <c r="S220" s="159" t="n"/>
-      <c r="T220" s="350" t="inlineStr">
+      <c r="T220" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -17086,7 +17087,7 @@
           <t>金５</t>
         </is>
       </c>
-      <c r="O221" s="349" t="inlineStr">
+      <c r="O221" s="350" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -17195,22 +17196,22 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="E224" s="350" t="inlineStr">
+      <c r="E224" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="F224" s="350" t="inlineStr">
+      <c r="F224" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G224" s="350" t="inlineStr">
+      <c r="G224" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="H224" s="350" t="inlineStr">
+      <c r="H224" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -17225,22 +17226,22 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="K224" s="350" t="inlineStr">
+      <c r="K224" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="L224" s="350" t="inlineStr">
+      <c r="L224" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="M224" s="350" t="inlineStr">
+      <c r="M224" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="N224" s="350" t="inlineStr">
+      <c r="N224" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -17255,22 +17256,22 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="Q224" s="350" t="inlineStr">
+      <c r="Q224" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="R224" s="350" t="inlineStr">
+      <c r="R224" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="S224" s="350" t="inlineStr">
+      <c r="S224" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="T224" s="350" t="inlineStr">
+      <c r="T224" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -17305,12 +17306,12 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="F225" s="350" t="inlineStr">
-        <is>
-          <t>木３</t>
-        </is>
-      </c>
-      <c r="G225" s="350" t="inlineStr">
+      <c r="F225" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
+        </is>
+      </c>
+      <c r="G225" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
@@ -17327,12 +17328,12 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="L225" s="350" t="inlineStr">
-        <is>
-          <t>木３</t>
-        </is>
-      </c>
-      <c r="M225" s="350" t="inlineStr">
+      <c r="L225" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
+        </is>
+      </c>
+      <c r="M225" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
@@ -17349,12 +17350,12 @@
           <t>火２</t>
         </is>
       </c>
-      <c r="R225" s="350" t="inlineStr">
-        <is>
-          <t>木３</t>
-        </is>
-      </c>
-      <c r="S225" s="350" t="inlineStr">
+      <c r="R225" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
+        </is>
+      </c>
+      <c r="S225" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
@@ -17381,12 +17382,12 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="E226" s="350" t="inlineStr">
+      <c r="E226" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F226" s="350" t="inlineStr">
+      <c r="F226" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -17403,12 +17404,12 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="K226" s="350" t="inlineStr">
+      <c r="K226" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L226" s="350" t="inlineStr">
+      <c r="L226" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -17425,12 +17426,12 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="Q226" s="350" t="inlineStr">
+      <c r="Q226" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R226" s="350" t="inlineStr">
+      <c r="R226" s="349" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -17462,17 +17463,17 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="E227" s="350" t="inlineStr">
-        <is>
-          <t>月２</t>
-        </is>
-      </c>
-      <c r="F227" s="350" t="inlineStr">
+      <c r="E227" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="F227" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G227" s="350" t="inlineStr">
+      <c r="G227" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
@@ -17484,17 +17485,17 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="K227" s="350" t="inlineStr">
-        <is>
-          <t>月２</t>
-        </is>
-      </c>
-      <c r="L227" s="350" t="inlineStr">
+      <c r="K227" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="L227" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="M227" s="350" t="inlineStr">
+      <c r="M227" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
@@ -17506,17 +17507,17 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="Q227" s="350" t="inlineStr">
-        <is>
-          <t>月２</t>
-        </is>
-      </c>
-      <c r="R227" s="350" t="inlineStr">
+      <c r="Q227" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="R227" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="S227" s="350" t="inlineStr">
+      <c r="S227" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
@@ -17543,7 +17544,7 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="E228" s="368" t="inlineStr">
+      <c r="E228" s="369" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -17565,7 +17566,7 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="K228" s="368" t="inlineStr">
+      <c r="K228" s="369" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -17587,7 +17588,7 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="Q228" s="368" t="inlineStr">
+      <c r="Q228" s="369" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -17682,29 +17683,29 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="E231" s="350" t="inlineStr">
+      <c r="E231" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="F231" s="350" t="inlineStr">
+      <c r="F231" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="G231" s="350" t="inlineStr">
+      <c r="G231" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="H231" s="350" t="inlineStr">
+      <c r="H231" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="I231" s="357" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="I231" s="180" t="inlineStr">
+        <is>
+          <t>月６</t>
         </is>
       </c>
       <c r="J231" s="158" t="inlineStr">
@@ -17712,29 +17713,29 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="K231" s="350" t="inlineStr">
+      <c r="K231" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="L231" s="350" t="inlineStr">
+      <c r="L231" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="M231" s="350" t="inlineStr">
+      <c r="M231" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="N231" s="350" t="inlineStr">
+      <c r="N231" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="O231" s="358" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="O231" s="77" t="inlineStr">
+        <is>
+          <t>月６</t>
         </is>
       </c>
       <c r="P231" s="158" t="inlineStr">
@@ -17742,29 +17743,29 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="Q231" s="350" t="inlineStr">
+      <c r="Q231" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="R231" s="350" t="inlineStr">
+      <c r="R231" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S231" s="350" t="inlineStr">
+      <c r="S231" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="T231" s="350" t="inlineStr">
+      <c r="T231" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="U231" s="358" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="U231" s="77" t="inlineStr">
+        <is>
+          <t>月６</t>
         </is>
       </c>
     </row>
@@ -17787,22 +17788,22 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="E232" s="350" t="inlineStr">
+      <c r="E232" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F232" s="350" t="inlineStr">
+      <c r="F232" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="G232" s="350" t="inlineStr">
+      <c r="G232" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="H232" s="350" t="inlineStr">
+      <c r="H232" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -17817,22 +17818,22 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="K232" s="350" t="inlineStr">
+      <c r="K232" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L232" s="350" t="inlineStr">
+      <c r="L232" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="M232" s="350" t="inlineStr">
+      <c r="M232" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="N232" s="350" t="inlineStr">
+      <c r="N232" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -17847,22 +17848,22 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="Q232" s="350" t="inlineStr">
+      <c r="Q232" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R232" s="350" t="inlineStr">
+      <c r="R232" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="S232" s="350" t="inlineStr">
+      <c r="S232" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="T232" s="350" t="inlineStr">
+      <c r="T232" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -17963,9 +17964,9 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="E235" s="159" t="inlineStr">
-        <is>
-          <t>金２</t>
+      <c r="E235" s="349" t="inlineStr">
+        <is>
+          <t>金５</t>
         </is>
       </c>
       <c r="F235" s="159" t="inlineStr">
@@ -17973,7 +17974,7 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="G235" s="350" t="inlineStr">
+      <c r="G235" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -17993,9 +17994,9 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="K235" s="159" t="inlineStr">
-        <is>
-          <t>金２</t>
+      <c r="K235" s="349" t="inlineStr">
+        <is>
+          <t>金５</t>
         </is>
       </c>
       <c r="L235" s="159" t="inlineStr">
@@ -18003,14 +18004,14 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="M235" s="350" t="inlineStr">
+      <c r="M235" s="349" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="N235" s="159" t="inlineStr">
-        <is>
-          <t>金５</t>
+      <c r="N235" s="349" t="inlineStr">
+        <is>
+          <t>月３</t>
         </is>
       </c>
       <c r="O235" s="77" t="inlineStr">
@@ -18520,92 +18521,92 @@
         </is>
       </c>
       <c r="C245" s="41" t="n"/>
-      <c r="D245" s="356" t="inlineStr">
+      <c r="D245" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="E245" s="350" t="inlineStr">
+      <c r="E245" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="F245" s="350" t="inlineStr">
+      <c r="F245" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="G245" s="350" t="inlineStr">
+      <c r="G245" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="H245" s="350" t="inlineStr">
+      <c r="H245" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="I245" s="357" t="inlineStr">
+      <c r="I245" s="351" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
       </c>
-      <c r="J245" s="356" t="inlineStr">
+      <c r="J245" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="K245" s="350" t="inlineStr">
+      <c r="K245" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="L245" s="350" t="inlineStr">
+      <c r="L245" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="M245" s="350" t="inlineStr">
+      <c r="M245" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="N245" s="350" t="inlineStr">
+      <c r="N245" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="O245" s="349" t="inlineStr">
+      <c r="O245" s="350" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
       </c>
-      <c r="P245" s="356" t="inlineStr">
+      <c r="P245" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="Q245" s="350" t="inlineStr">
+      <c r="Q245" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="R245" s="350" t="inlineStr">
+      <c r="R245" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S245" s="350" t="inlineStr">
+      <c r="S245" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="T245" s="350" t="inlineStr">
+      <c r="T245" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="U245" s="358" t="inlineStr">
+      <c r="U245" s="352" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -18621,92 +18622,92 @@
         </is>
       </c>
       <c r="C246" s="41" t="n"/>
-      <c r="D246" s="351" t="inlineStr">
+      <c r="D246" s="353" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="E246" s="352" t="inlineStr">
+      <c r="E246" s="354" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="F246" s="352" t="inlineStr">
+      <c r="F246" s="354" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="G246" s="352" t="inlineStr">
+      <c r="G246" s="354" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="H246" s="352" t="inlineStr">
+      <c r="H246" s="354" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="I246" s="388" t="inlineStr">
+      <c r="I246" s="389" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="J246" s="351" t="inlineStr">
+      <c r="J246" s="353" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="K246" s="352" t="inlineStr">
+      <c r="K246" s="354" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="L246" s="352" t="inlineStr">
+      <c r="L246" s="354" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="M246" s="352" t="inlineStr">
+      <c r="M246" s="354" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="N246" s="352" t="inlineStr">
+      <c r="N246" s="354" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="O246" s="389" t="inlineStr">
+      <c r="O246" s="390" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="P246" s="351" t="inlineStr">
+      <c r="P246" s="353" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="Q246" s="352" t="inlineStr">
+      <c r="Q246" s="354" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="R246" s="352" t="inlineStr">
+      <c r="R246" s="354" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="S246" s="352" t="inlineStr">
+      <c r="S246" s="354" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="T246" s="352" t="inlineStr">
+      <c r="T246" s="354" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="U246" s="389" t="inlineStr">
+      <c r="U246" s="390" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -18888,66 +18889,66 @@
           <t>保護者会(全)</t>
         </is>
       </c>
-      <c r="D249" s="356" t="inlineStr">
+      <c r="D249" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E249" s="350" t="inlineStr">
+      <c r="E249" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F249" s="350" t="inlineStr">
+      <c r="F249" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G249" s="350" t="inlineStr">
+      <c r="G249" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
       <c r="H249" s="159" t="n"/>
       <c r="I249" s="180" t="n"/>
-      <c r="J249" s="356" t="inlineStr">
+      <c r="J249" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="K249" s="350" t="inlineStr">
+      <c r="K249" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L249" s="350" t="inlineStr">
+      <c r="L249" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="M249" s="350" t="inlineStr">
+      <c r="M249" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
       <c r="N249" s="159" t="n"/>
       <c r="O249" s="77" t="n"/>
-      <c r="P249" s="356" t="inlineStr">
+      <c r="P249" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="Q249" s="350" t="inlineStr">
+      <c r="Q249" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="R249" s="350" t="inlineStr">
+      <c r="R249" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="S249" s="350" t="inlineStr">
+      <c r="S249" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
@@ -19027,66 +19028,66 @@
           <t>保護者会(全)</t>
         </is>
       </c>
-      <c r="D252" s="356" t="inlineStr">
+      <c r="D252" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="E252" s="350" t="inlineStr">
-        <is>
-          <t>火２</t>
-        </is>
-      </c>
-      <c r="F252" s="350" t="inlineStr">
+      <c r="E252" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="F252" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="G252" s="350" t="inlineStr">
+      <c r="G252" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
       <c r="H252" s="159" t="n"/>
       <c r="I252" s="180" t="n"/>
-      <c r="J252" s="356" t="inlineStr">
+      <c r="J252" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="K252" s="350" t="inlineStr">
-        <is>
-          <t>火２</t>
-        </is>
-      </c>
-      <c r="L252" s="350" t="inlineStr">
+      <c r="K252" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="L252" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="M252" s="350" t="inlineStr">
+      <c r="M252" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
       <c r="N252" s="159" t="n"/>
       <c r="O252" s="77" t="n"/>
-      <c r="P252" s="356" t="inlineStr">
+      <c r="P252" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="Q252" s="350" t="inlineStr">
-        <is>
-          <t>火２</t>
-        </is>
-      </c>
-      <c r="R252" s="350" t="inlineStr">
+      <c r="Q252" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="R252" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S252" s="350" t="inlineStr">
+      <c r="S252" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
@@ -19108,22 +19109,22 @@
           <t>通知表(仮)提出</t>
         </is>
       </c>
-      <c r="D253" s="356" t="inlineStr">
+      <c r="D253" s="358" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="E253" s="350" t="inlineStr">
+      <c r="E253" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="F253" s="350" t="inlineStr">
+      <c r="F253" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="G253" s="350" t="inlineStr">
+      <c r="G253" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
@@ -19138,22 +19139,22 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="J253" s="356" t="inlineStr">
+      <c r="J253" s="358" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="K253" s="350" t="inlineStr">
+      <c r="K253" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="L253" s="350" t="inlineStr">
+      <c r="L253" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="M253" s="350" t="inlineStr">
+      <c r="M253" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
@@ -19168,22 +19169,22 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="P253" s="356" t="inlineStr">
+      <c r="P253" s="358" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="Q253" s="350" t="inlineStr">
+      <c r="Q253" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="R253" s="350" t="inlineStr">
+      <c r="R253" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="S253" s="350" t="inlineStr">
+      <c r="S253" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
@@ -19419,27 +19420,27 @@
         </is>
       </c>
       <c r="C256" s="41" t="n"/>
-      <c r="D256" s="386" t="inlineStr">
+      <c r="D256" s="387" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="E256" s="368" t="inlineStr">
+      <c r="E256" s="369" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F256" s="350" t="inlineStr">
+      <c r="F256" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G256" s="350" t="inlineStr">
+      <c r="G256" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H256" s="350" t="inlineStr">
+      <c r="H256" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -19449,27 +19450,27 @@
           <t>金６</t>
         </is>
       </c>
-      <c r="J256" s="386" t="inlineStr">
+      <c r="J256" s="387" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="K256" s="368" t="inlineStr">
+      <c r="K256" s="369" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L256" s="350" t="inlineStr">
+      <c r="L256" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="M256" s="350" t="inlineStr">
+      <c r="M256" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="N256" s="350" t="inlineStr">
+      <c r="N256" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -19479,27 +19480,27 @@
           <t>金６</t>
         </is>
       </c>
-      <c r="P256" s="386" t="inlineStr">
+      <c r="P256" s="387" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="Q256" s="368" t="inlineStr">
+      <c r="Q256" s="369" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="R256" s="350" t="inlineStr">
+      <c r="R256" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="S256" s="350" t="inlineStr">
+      <c r="S256" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="T256" s="350" t="inlineStr">
+      <c r="T256" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -19587,17 +19588,17 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="E259" s="350" t="inlineStr">
+      <c r="E259" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="F259" s="350" t="inlineStr">
+      <c r="F259" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="G259" s="350" t="inlineStr">
+      <c r="G259" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
@@ -19617,17 +19618,17 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="K259" s="350" t="inlineStr">
+      <c r="K259" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="L259" s="350" t="inlineStr">
+      <c r="L259" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="M259" s="350" t="inlineStr">
+      <c r="M259" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
@@ -19647,17 +19648,17 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="Q259" s="350" t="inlineStr">
+      <c r="Q259" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="R259" s="350" t="inlineStr">
+      <c r="R259" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S259" s="350" t="inlineStr">
+      <c r="S259" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
@@ -19688,29 +19689,29 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="E260" s="350" t="inlineStr">
+      <c r="E260" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="F260" s="350" t="inlineStr">
+      <c r="F260" s="349" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="G260" s="350" t="inlineStr">
+      <c r="G260" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="H260" s="367" t="inlineStr">
+      <c r="H260" s="368" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="I260" s="180" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="I260" s="351" t="inlineStr">
+        <is>
+          <t>金３</t>
         </is>
       </c>
       <c r="J260" s="158" t="inlineStr">
@@ -19718,29 +19719,29 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="K260" s="350" t="inlineStr">
+      <c r="K260" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="L260" s="350" t="inlineStr">
+      <c r="L260" s="349" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="M260" s="350" t="inlineStr">
+      <c r="M260" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="N260" s="350" t="inlineStr">
+      <c r="N260" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="O260" s="77" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="O260" s="352" t="inlineStr">
+        <is>
+          <t>金３</t>
         </is>
       </c>
       <c r="P260" s="158" t="inlineStr">
@@ -19748,29 +19749,29 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="Q260" s="350" t="inlineStr">
+      <c r="Q260" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="R260" s="350" t="inlineStr">
+      <c r="R260" s="349" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="S260" s="350" t="inlineStr">
+      <c r="S260" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="T260" s="350" t="inlineStr">
+      <c r="T260" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="U260" s="77" t="inlineStr">
-        <is>
-          <t>火６</t>
+      <c r="U260" s="352" t="inlineStr">
+        <is>
+          <t>金３</t>
         </is>
       </c>
     </row>
@@ -19793,89 +19794,89 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="E261" s="350" t="inlineStr">
+      <c r="E261" s="349" t="inlineStr">
+        <is>
+          <t>火６</t>
+        </is>
+      </c>
+      <c r="F261" s="159" t="inlineStr">
+        <is>
+          <t>水３</t>
+        </is>
+      </c>
+      <c r="G261" s="159" t="inlineStr">
+        <is>
+          <t>水４</t>
+        </is>
+      </c>
+      <c r="H261" s="159" t="inlineStr">
+        <is>
+          <t>水５</t>
+        </is>
+      </c>
+      <c r="I261" s="180" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
       </c>
-      <c r="F261" s="159" t="inlineStr">
+      <c r="J261" s="158" t="inlineStr">
+        <is>
+          <t>水１</t>
+        </is>
+      </c>
+      <c r="K261" s="349" t="inlineStr">
+        <is>
+          <t>火６</t>
+        </is>
+      </c>
+      <c r="L261" s="159" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G261" s="159" t="inlineStr">
+      <c r="M261" s="159" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="H261" s="159" t="inlineStr">
+      <c r="N261" s="159" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
       </c>
-      <c r="I261" s="357" t="inlineStr">
+      <c r="O261" s="77" t="inlineStr">
+        <is>
+          <t>水６</t>
+        </is>
+      </c>
+      <c r="P261" s="158" t="inlineStr">
+        <is>
+          <t>水１</t>
+        </is>
+      </c>
+      <c r="Q261" s="349" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
       </c>
-      <c r="J261" s="158" t="inlineStr">
-        <is>
-          <t>水１</t>
-        </is>
-      </c>
-      <c r="K261" s="350" t="inlineStr">
+      <c r="R261" s="159" t="inlineStr">
+        <is>
+          <t>水３</t>
+        </is>
+      </c>
+      <c r="S261" s="159" t="inlineStr">
+        <is>
+          <t>水４</t>
+        </is>
+      </c>
+      <c r="T261" s="159" t="inlineStr">
+        <is>
+          <t>水５</t>
+        </is>
+      </c>
+      <c r="U261" s="77" t="inlineStr">
         <is>
           <t>水６</t>
-        </is>
-      </c>
-      <c r="L261" s="159" t="inlineStr">
-        <is>
-          <t>水３</t>
-        </is>
-      </c>
-      <c r="M261" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
-        </is>
-      </c>
-      <c r="N261" s="159" t="inlineStr">
-        <is>
-          <t>水５</t>
-        </is>
-      </c>
-      <c r="O261" s="349" t="inlineStr">
-        <is>
-          <t>火６</t>
-        </is>
-      </c>
-      <c r="P261" s="158" t="inlineStr">
-        <is>
-          <t>水１</t>
-        </is>
-      </c>
-      <c r="Q261" s="350" t="inlineStr">
-        <is>
-          <t>水６</t>
-        </is>
-      </c>
-      <c r="R261" s="159" t="inlineStr">
-        <is>
-          <t>水３</t>
-        </is>
-      </c>
-      <c r="S261" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
-        </is>
-      </c>
-      <c r="T261" s="159" t="inlineStr">
-        <is>
-          <t>水５</t>
-        </is>
-      </c>
-      <c r="U261" s="358" t="inlineStr">
-        <is>
-          <t>火６</t>
         </is>
       </c>
     </row>
@@ -19991,22 +19992,22 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="E263" s="368" t="inlineStr">
+      <c r="E263" s="369" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="F263" s="350" t="inlineStr">
+      <c r="F263" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="G263" s="350" t="inlineStr">
+      <c r="G263" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="H263" s="350" t="inlineStr">
+      <c r="H263" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -20021,27 +20022,27 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="K263" s="368" t="inlineStr">
+      <c r="K263" s="369" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="L263" s="350" t="inlineStr">
+      <c r="L263" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="M263" s="350" t="inlineStr">
+      <c r="M263" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="N263" s="350" t="inlineStr">
+      <c r="N263" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="O263" s="77" t="inlineStr">
+      <c r="O263" s="350" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -20051,22 +20052,22 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="Q263" s="368" t="inlineStr">
+      <c r="Q263" s="369" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="R263" s="350" t="inlineStr">
+      <c r="R263" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S263" s="350" t="inlineStr">
+      <c r="S263" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="T263" s="350" t="inlineStr">
+      <c r="T263" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -20174,7 +20175,7 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="I266" s="357" t="inlineStr">
+      <c r="I266" s="351" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -20204,7 +20205,7 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="O266" s="358" t="inlineStr">
+      <c r="O266" s="352" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -20234,7 +20235,7 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="U266" s="358" t="inlineStr">
+      <c r="U266" s="352" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -20255,22 +20256,22 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="E267" s="350" t="inlineStr">
+      <c r="E267" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="F267" s="350" t="inlineStr">
+      <c r="F267" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="G267" s="350" t="inlineStr">
+      <c r="G267" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="H267" s="350" t="inlineStr">
+      <c r="H267" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
@@ -20285,22 +20286,22 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="K267" s="350" t="inlineStr">
+      <c r="K267" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="L267" s="350" t="inlineStr">
+      <c r="L267" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="M267" s="350" t="inlineStr">
+      <c r="M267" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="N267" s="350" t="inlineStr">
+      <c r="N267" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
@@ -20315,22 +20316,22 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="Q267" s="350" t="inlineStr">
+      <c r="Q267" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="R267" s="350" t="inlineStr">
+      <c r="R267" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="S267" s="350" t="inlineStr">
+      <c r="S267" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="T267" s="350" t="inlineStr">
+      <c r="T267" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
@@ -20366,14 +20367,14 @@
         </is>
       </c>
       <c r="F268" s="159" t="n"/>
-      <c r="G268" s="350" t="inlineStr">
+      <c r="G268" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
+        </is>
+      </c>
+      <c r="H268" s="349" t="inlineStr">
         <is>
           <t>月６</t>
-        </is>
-      </c>
-      <c r="H268" s="159" t="inlineStr">
-        <is>
-          <t>水５</t>
         </is>
       </c>
       <c r="I268" s="180" t="n"/>
@@ -20392,9 +20393,9 @@
           <t>水３</t>
         </is>
       </c>
-      <c r="M268" s="350" t="inlineStr">
-        <is>
-          <t>月６</t>
+      <c r="M268" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
         </is>
       </c>
       <c r="N268" s="159" t="n"/>
@@ -20410,14 +20411,14 @@
         </is>
       </c>
       <c r="R268" s="159" t="n"/>
-      <c r="S268" s="350" t="inlineStr">
+      <c r="S268" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
+        </is>
+      </c>
+      <c r="T268" s="349" t="inlineStr">
         <is>
           <t>月６</t>
-        </is>
-      </c>
-      <c r="T268" s="159" t="inlineStr">
-        <is>
-          <t>水５</t>
         </is>
       </c>
       <c r="U268" s="77" t="n"/>
@@ -21140,22 +21141,22 @@
         </is>
       </c>
       <c r="D277" s="381" t="n"/>
-      <c r="E277" s="353" t="n"/>
-      <c r="F277" s="353" t="n"/>
-      <c r="G277" s="353" t="n"/>
-      <c r="H277" s="353" t="n"/>
+      <c r="E277" s="355" t="n"/>
+      <c r="F277" s="355" t="n"/>
+      <c r="G277" s="355" t="n"/>
+      <c r="H277" s="355" t="n"/>
       <c r="I277" s="268" t="n"/>
       <c r="J277" s="381" t="n"/>
-      <c r="K277" s="353" t="n"/>
-      <c r="L277" s="353" t="n"/>
-      <c r="M277" s="353" t="n"/>
-      <c r="N277" s="353" t="n"/>
+      <c r="K277" s="355" t="n"/>
+      <c r="L277" s="355" t="n"/>
+      <c r="M277" s="355" t="n"/>
+      <c r="N277" s="355" t="n"/>
       <c r="O277" s="284" t="n"/>
       <c r="P277" s="381" t="n"/>
-      <c r="Q277" s="353" t="n"/>
-      <c r="R277" s="353" t="n"/>
-      <c r="S277" s="353" t="n"/>
-      <c r="T277" s="353" t="n"/>
+      <c r="Q277" s="355" t="n"/>
+      <c r="R277" s="355" t="n"/>
+      <c r="S277" s="355" t="n"/>
+      <c r="T277" s="355" t="n"/>
       <c r="U277" s="284" t="n"/>
     </row>
     <row r="278">
@@ -21511,7 +21512,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="I288" s="357" t="inlineStr">
+      <c r="I288" s="351" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -21541,7 +21542,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="O288" s="358" t="inlineStr">
+      <c r="O288" s="352" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -21583,69 +21584,69 @@
           <t>保護者会(3年)・【私立専修推薦･特色入試】</t>
         </is>
       </c>
-      <c r="D289" s="158" t="inlineStr">
+      <c r="D289" s="358" t="inlineStr">
+        <is>
+          <t>水６</t>
+        </is>
+      </c>
+      <c r="E289" s="159" t="inlineStr">
+        <is>
+          <t>水２</t>
+        </is>
+      </c>
+      <c r="F289" s="159" t="inlineStr">
+        <is>
+          <t>水３</t>
+        </is>
+      </c>
+      <c r="G289" s="159" t="inlineStr">
+        <is>
+          <t>水４</t>
+        </is>
+      </c>
+      <c r="H289" s="159" t="inlineStr">
+        <is>
+          <t>水５</t>
+        </is>
+      </c>
+      <c r="I289" s="351" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="E289" s="159" t="inlineStr">
+      <c r="J289" s="358" t="inlineStr">
+        <is>
+          <t>水６</t>
+        </is>
+      </c>
+      <c r="K289" s="159" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="F289" s="159" t="inlineStr">
+      <c r="L289" s="159" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G289" s="159" t="inlineStr">
+      <c r="M289" s="159" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="H289" s="159" t="inlineStr">
+      <c r="N289" s="159" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
       </c>
-      <c r="I289" s="180" t="inlineStr">
+      <c r="O289" s="352" t="inlineStr">
+        <is>
+          <t>水１</t>
+        </is>
+      </c>
+      <c r="P289" s="358" t="inlineStr">
         <is>
           <t>水６</t>
-        </is>
-      </c>
-      <c r="J289" s="158" t="inlineStr">
-        <is>
-          <t>水１</t>
-        </is>
-      </c>
-      <c r="K289" s="159" t="inlineStr">
-        <is>
-          <t>水２</t>
-        </is>
-      </c>
-      <c r="L289" s="159" t="inlineStr">
-        <is>
-          <t>水３</t>
-        </is>
-      </c>
-      <c r="M289" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
-        </is>
-      </c>
-      <c r="N289" s="159" t="inlineStr">
-        <is>
-          <t>水５</t>
-        </is>
-      </c>
-      <c r="O289" s="77" t="inlineStr">
-        <is>
-          <t>水６</t>
-        </is>
-      </c>
-      <c r="P289" s="158" t="inlineStr">
-        <is>
-          <t>水１</t>
         </is>
       </c>
       <c r="Q289" s="159" t="inlineStr">
@@ -21774,74 +21775,74 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="E291" s="350" t="inlineStr">
+      <c r="E291" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F291" s="159" t="inlineStr">
+      <c r="F291" s="349" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="G291" s="159" t="inlineStr">
+        <is>
+          <t>金４</t>
+        </is>
+      </c>
+      <c r="H291" s="369" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="G291" s="159" t="inlineStr">
+      <c r="I291" s="180" t="inlineStr">
+        <is>
+          <t>金６</t>
+        </is>
+      </c>
+      <c r="J291" s="189" t="inlineStr">
+        <is>
+          <t>金１</t>
+        </is>
+      </c>
+      <c r="K291" s="349" t="inlineStr">
+        <is>
+          <t>月２</t>
+        </is>
+      </c>
+      <c r="L291" s="349" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="M291" s="159" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="H291" s="190" t="inlineStr">
+      <c r="N291" s="369" t="inlineStr">
+        <is>
+          <t>金３</t>
+        </is>
+      </c>
+      <c r="O291" s="77" t="inlineStr">
+        <is>
+          <t>金６</t>
+        </is>
+      </c>
+      <c r="P291" s="189" t="inlineStr">
+        <is>
+          <t>金１</t>
+        </is>
+      </c>
+      <c r="Q291" s="349" t="inlineStr">
+        <is>
+          <t>月２</t>
+        </is>
+      </c>
+      <c r="R291" s="349" t="inlineStr">
         <is>
           <t>金５</t>
-        </is>
-      </c>
-      <c r="I291" s="180" t="inlineStr">
-        <is>
-          <t>金６</t>
-        </is>
-      </c>
-      <c r="J291" s="189" t="inlineStr">
-        <is>
-          <t>金１</t>
-        </is>
-      </c>
-      <c r="K291" s="350" t="inlineStr">
-        <is>
-          <t>月２</t>
-        </is>
-      </c>
-      <c r="L291" s="159" t="inlineStr">
-        <is>
-          <t>金３</t>
-        </is>
-      </c>
-      <c r="M291" s="159" t="inlineStr">
-        <is>
-          <t>金４</t>
-        </is>
-      </c>
-      <c r="N291" s="190" t="inlineStr">
-        <is>
-          <t>金５</t>
-        </is>
-      </c>
-      <c r="O291" s="77" t="inlineStr">
-        <is>
-          <t>金６</t>
-        </is>
-      </c>
-      <c r="P291" s="189" t="inlineStr">
-        <is>
-          <t>金１</t>
-        </is>
-      </c>
-      <c r="Q291" s="350" t="inlineStr">
-        <is>
-          <t>月２</t>
-        </is>
-      </c>
-      <c r="R291" s="159" t="inlineStr">
-        <is>
-          <t>金３</t>
         </is>
       </c>
       <c r="S291" s="159" t="inlineStr">
@@ -22050,7 +22051,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="I295" s="357" t="inlineStr">
+      <c r="I295" s="351" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -22080,7 +22081,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="O295" s="358" t="inlineStr">
+      <c r="O295" s="352" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -22110,7 +22111,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="U295" s="358" t="inlineStr">
+      <c r="U295" s="352" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -22130,34 +22131,34 @@
           <t>職場体験（2年）・【私立専修一般入試】</t>
         </is>
       </c>
-      <c r="D296" s="356" t="inlineStr">
+      <c r="D296" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E296" s="350" t="inlineStr">
+      <c r="E296" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="F296" s="349" t="inlineStr">
+        <is>
+          <t>月３</t>
+        </is>
+      </c>
+      <c r="G296" s="159" t="inlineStr">
+        <is>
+          <t>水４</t>
+        </is>
+      </c>
+      <c r="H296" s="349" t="inlineStr">
+        <is>
+          <t>月６</t>
+        </is>
+      </c>
+      <c r="I296" s="180" t="inlineStr">
         <is>
           <t>水６</t>
-        </is>
-      </c>
-      <c r="F296" s="350" t="inlineStr">
-        <is>
-          <t>月３</t>
-        </is>
-      </c>
-      <c r="G296" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
-        </is>
-      </c>
-      <c r="H296" s="350" t="inlineStr">
-        <is>
-          <t>月５</t>
-        </is>
-      </c>
-      <c r="I296" s="357" t="inlineStr">
-        <is>
-          <t>月６</t>
         </is>
       </c>
       <c r="J296" s="158" t="n"/>
@@ -22166,17 +22167,17 @@
       <c r="M296" s="159" t="n"/>
       <c r="N296" s="159" t="n"/>
       <c r="O296" s="77" t="n"/>
-      <c r="P296" s="356" t="inlineStr">
+      <c r="P296" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="Q296" s="350" t="inlineStr">
-        <is>
-          <t>水６</t>
-        </is>
-      </c>
-      <c r="R296" s="350" t="inlineStr">
+      <c r="Q296" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="R296" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -22199,7 +22200,7 @@
           <t>職場訪問(1年)・職場体験（2年）・【私立専修一般入試】</t>
         </is>
       </c>
-      <c r="D297" s="356" t="inlineStr">
+      <c r="D297" s="358" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -22231,7 +22232,7 @@
       <c r="M297" s="191" t="n"/>
       <c r="N297" s="191" t="n"/>
       <c r="O297" s="192" t="n"/>
-      <c r="P297" s="356" t="inlineStr">
+      <c r="P297" s="358" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -22289,9 +22290,9 @@
           <t>金５</t>
         </is>
       </c>
-      <c r="I298" s="180" t="inlineStr">
-        <is>
-          <t>金６</t>
+      <c r="I298" s="351" t="inlineStr">
+        <is>
+          <t>水２</t>
         </is>
       </c>
       <c r="J298" s="193" t="inlineStr">
@@ -22319,9 +22320,9 @@
           <t>金５</t>
         </is>
       </c>
-      <c r="O298" s="390" t="inlineStr">
-        <is>
-          <t>金６</t>
+      <c r="O298" s="391" t="inlineStr">
+        <is>
+          <t>水２</t>
         </is>
       </c>
       <c r="P298" s="189" t="inlineStr">
@@ -22429,7 +22430,7 @@
           <t>月２</t>
         </is>
       </c>
-      <c r="F301" s="350" t="inlineStr">
+      <c r="F301" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
@@ -22444,7 +22445,7 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="I301" s="357" t="inlineStr">
+      <c r="I301" s="351" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -22459,7 +22460,7 @@
           <t>月２</t>
         </is>
       </c>
-      <c r="L301" s="350" t="inlineStr">
+      <c r="L301" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
@@ -22474,7 +22475,7 @@
           <t>月５</t>
         </is>
       </c>
-      <c r="O301" s="358" t="inlineStr">
+      <c r="O301" s="350" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -22501,27 +22502,27 @@
 　若宮高等支援学校入学者選考】</t>
         </is>
       </c>
-      <c r="D302" s="356" t="inlineStr">
+      <c r="D302" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="E302" s="350" t="inlineStr">
+      <c r="E302" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="F302" s="350" t="inlineStr">
+      <c r="F302" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G302" s="350" t="inlineStr">
+      <c r="G302" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="H302" s="350" t="inlineStr">
+      <c r="H302" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -22531,27 +22532,27 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="J302" s="356" t="inlineStr">
+      <c r="J302" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="K302" s="350" t="inlineStr">
+      <c r="K302" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="L302" s="350" t="inlineStr">
+      <c r="L302" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="M302" s="350" t="inlineStr">
+      <c r="M302" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="N302" s="350" t="inlineStr">
+      <c r="N302" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -22561,27 +22562,27 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="P302" s="391" t="inlineStr">
+      <c r="P302" s="392" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="Q302" s="373" t="inlineStr">
+      <c r="Q302" s="360" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="R302" s="373" t="inlineStr">
+      <c r="R302" s="360" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="S302" s="373" t="inlineStr">
+      <c r="S302" s="360" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="T302" s="373" t="inlineStr">
+      <c r="T302" s="360" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -22606,27 +22607,27 @@
           <t>選挙管理委員会・【通信制前期合格発表】</t>
         </is>
       </c>
-      <c r="D303" s="356" t="inlineStr">
+      <c r="D303" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="E303" s="350" t="inlineStr">
+      <c r="E303" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F303" s="350" t="inlineStr">
+      <c r="F303" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="G303" s="350" t="inlineStr">
+      <c r="G303" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="H303" s="350" t="inlineStr">
+      <c r="H303" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -22636,27 +22637,27 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="J303" s="356" t="inlineStr">
+      <c r="J303" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="K303" s="350" t="inlineStr">
+      <c r="K303" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L303" s="350" t="inlineStr">
+      <c r="L303" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="M303" s="350" t="inlineStr">
+      <c r="M303" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="N303" s="350" t="inlineStr">
+      <c r="N303" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -22666,27 +22667,27 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="P303" s="356" t="inlineStr">
+      <c r="P303" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="Q303" s="350" t="inlineStr">
+      <c r="Q303" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R303" s="350" t="inlineStr">
+      <c r="R303" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="S303" s="350" t="inlineStr">
+      <c r="S303" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="T303" s="350" t="inlineStr">
+      <c r="T303" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -22707,79 +22708,79 @@
         </is>
       </c>
       <c r="C304" s="41" t="n"/>
-      <c r="D304" s="356" t="inlineStr">
+      <c r="D304" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E304" s="350" t="inlineStr">
+      <c r="E304" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F304" s="350" t="inlineStr">
+      <c r="F304" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G304" s="350" t="inlineStr">
+      <c r="G304" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H304" s="350" t="inlineStr">
+      <c r="H304" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
       <c r="I304" s="180" t="n"/>
-      <c r="J304" s="356" t="inlineStr">
+      <c r="J304" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="K304" s="350" t="inlineStr">
+      <c r="K304" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L304" s="350" t="inlineStr">
+      <c r="L304" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="M304" s="350" t="inlineStr">
+      <c r="M304" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="N304" s="350" t="inlineStr">
+      <c r="N304" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
       <c r="O304" s="77" t="n"/>
-      <c r="P304" s="356" t="inlineStr">
+      <c r="P304" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="Q304" s="350" t="inlineStr">
+      <c r="Q304" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="R304" s="350" t="inlineStr">
+      <c r="R304" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="S304" s="350" t="inlineStr">
+      <c r="S304" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="T304" s="350" t="inlineStr">
+      <c r="T304" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -22955,92 +22956,92 @@
         </is>
       </c>
       <c r="C308" s="41" t="n"/>
-      <c r="D308" s="392" t="inlineStr">
+      <c r="D308" s="393" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="E308" s="393" t="inlineStr">
+      <c r="E308" s="394" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="F308" s="393" t="inlineStr">
+      <c r="F308" s="394" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="G308" s="393" t="inlineStr">
+      <c r="G308" s="394" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="H308" s="393" t="inlineStr">
+      <c r="H308" s="394" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="I308" s="394" t="inlineStr">
+      <c r="I308" s="395" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="J308" s="392" t="inlineStr">
+      <c r="J308" s="393" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="K308" s="393" t="inlineStr">
+      <c r="K308" s="394" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="L308" s="393" t="inlineStr">
+      <c r="L308" s="394" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="M308" s="393" t="inlineStr">
+      <c r="M308" s="394" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="N308" s="393" t="inlineStr">
+      <c r="N308" s="394" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="O308" s="395" t="inlineStr">
+      <c r="O308" s="396" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="P308" s="392" t="inlineStr">
+      <c r="P308" s="393" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="Q308" s="393" t="inlineStr">
+      <c r="Q308" s="394" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="R308" s="393" t="inlineStr">
+      <c r="R308" s="394" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S308" s="393" t="inlineStr">
+      <c r="S308" s="394" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="T308" s="393" t="inlineStr">
+      <c r="T308" s="394" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
       </c>
-      <c r="U308" s="364" t="inlineStr">
+      <c r="U308" s="365" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -23056,27 +23057,27 @@
         </is>
       </c>
       <c r="C309" s="41" t="n"/>
-      <c r="D309" s="396" t="inlineStr">
+      <c r="D309" s="397" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="E309" s="396" t="inlineStr">
+      <c r="E309" s="397" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="F309" s="396" t="inlineStr">
+      <c r="F309" s="397" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G309" s="396" t="inlineStr">
+      <c r="G309" s="397" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="H309" s="396" t="inlineStr">
+      <c r="H309" s="397" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -23086,27 +23087,27 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="J309" s="397" t="inlineStr">
+      <c r="J309" s="398" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="K309" s="396" t="inlineStr">
+      <c r="K309" s="397" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="L309" s="396" t="inlineStr">
+      <c r="L309" s="397" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="M309" s="396" t="inlineStr">
+      <c r="M309" s="397" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="N309" s="396" t="inlineStr">
+      <c r="N309" s="397" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -23116,27 +23117,27 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="P309" s="397" t="inlineStr">
+      <c r="P309" s="398" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="Q309" s="396" t="inlineStr">
+      <c r="Q309" s="397" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="R309" s="396" t="inlineStr">
+      <c r="R309" s="397" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="S309" s="396" t="inlineStr">
+      <c r="S309" s="397" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="T309" s="396" t="inlineStr">
+      <c r="T309" s="397" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -23161,27 +23162,27 @@
           <t>第２回NCS会議</t>
         </is>
       </c>
-      <c r="D310" s="356" t="inlineStr">
+      <c r="D310" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="E310" s="350" t="inlineStr">
+      <c r="E310" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F310" s="350" t="inlineStr">
+      <c r="F310" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="G310" s="350" t="inlineStr">
+      <c r="G310" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="H310" s="350" t="inlineStr">
+      <c r="H310" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -23191,27 +23192,27 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="J310" s="356" t="inlineStr">
+      <c r="J310" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="K310" s="350" t="inlineStr">
+      <c r="K310" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L310" s="350" t="inlineStr">
+      <c r="L310" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="M310" s="350" t="inlineStr">
+      <c r="M310" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="N310" s="350" t="inlineStr">
+      <c r="N310" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -23221,27 +23222,27 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="P310" s="356" t="inlineStr">
+      <c r="P310" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="Q310" s="350" t="inlineStr">
+      <c r="Q310" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R310" s="350" t="inlineStr">
+      <c r="R310" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="S310" s="350" t="inlineStr">
+      <c r="S310" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="T310" s="350" t="inlineStr">
+      <c r="T310" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -23271,17 +23272,17 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="E311" s="350" t="inlineStr">
+      <c r="E311" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F311" s="350" t="inlineStr">
+      <c r="F311" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G311" s="350" t="inlineStr">
+      <c r="G311" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
@@ -23297,17 +23298,17 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="K311" s="350" t="inlineStr">
+      <c r="K311" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L311" s="350" t="inlineStr">
+      <c r="L311" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="M311" s="350" t="inlineStr">
+      <c r="M311" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
@@ -23323,17 +23324,17 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="Q311" s="350" t="inlineStr">
+      <c r="Q311" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="R311" s="350" t="inlineStr">
+      <c r="R311" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="S311" s="350" t="inlineStr">
+      <c r="S311" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
@@ -23518,27 +23519,27 @@
           <t>【公立推薦･特色合格発表】</t>
         </is>
       </c>
-      <c r="D315" s="356" t="inlineStr">
+      <c r="D315" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="E315" s="350" t="inlineStr">
+      <c r="E315" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="F315" s="350" t="inlineStr">
+      <c r="F315" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="G315" s="350" t="inlineStr">
+      <c r="G315" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="H315" s="350" t="inlineStr">
+      <c r="H315" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -23548,27 +23549,27 @@
           <t>月６</t>
         </is>
       </c>
-      <c r="J315" s="356" t="inlineStr">
+      <c r="J315" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="K315" s="350" t="inlineStr">
+      <c r="K315" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="L315" s="350" t="inlineStr">
+      <c r="L315" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="M315" s="350" t="inlineStr">
+      <c r="M315" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="N315" s="350" t="inlineStr">
+      <c r="N315" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -23578,27 +23579,27 @@
           <t>月６</t>
         </is>
       </c>
-      <c r="P315" s="356" t="inlineStr">
+      <c r="P315" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
       </c>
-      <c r="Q315" s="350" t="inlineStr">
+      <c r="Q315" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="R315" s="350" t="inlineStr">
+      <c r="R315" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
       </c>
-      <c r="S315" s="350" t="inlineStr">
+      <c r="S315" s="349" t="inlineStr">
         <is>
           <t>火４</t>
         </is>
       </c>
-      <c r="T315" s="350" t="inlineStr">
+      <c r="T315" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -23619,27 +23620,27 @@
         </is>
       </c>
       <c r="C316" s="41" t="n"/>
-      <c r="D316" s="356" t="inlineStr">
+      <c r="D316" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="E316" s="350" t="inlineStr">
+      <c r="E316" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="F316" s="350" t="inlineStr">
+      <c r="F316" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G316" s="350" t="inlineStr">
+      <c r="G316" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="H316" s="350" t="inlineStr">
+      <c r="H316" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -23649,57 +23650,57 @@
           <t>火６</t>
         </is>
       </c>
-      <c r="J316" s="356" t="inlineStr">
+      <c r="J316" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="K316" s="350" t="inlineStr">
+      <c r="K316" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="L316" s="350" t="inlineStr">
+      <c r="L316" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="M316" s="350" t="inlineStr">
+      <c r="M316" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="N316" s="350" t="inlineStr">
+      <c r="N316" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
       </c>
-      <c r="O316" s="349" t="inlineStr">
+      <c r="O316" s="350" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
       </c>
-      <c r="P316" s="356" t="inlineStr">
+      <c r="P316" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="Q316" s="350" t="inlineStr">
+      <c r="Q316" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="R316" s="350" t="inlineStr">
+      <c r="R316" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="S316" s="350" t="inlineStr">
+      <c r="S316" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="T316" s="350" t="inlineStr">
+      <c r="T316" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -23720,27 +23721,27 @@
         </is>
       </c>
       <c r="C317" s="41" t="n"/>
-      <c r="D317" s="356" t="inlineStr">
+      <c r="D317" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="E317" s="350" t="inlineStr">
+      <c r="E317" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F317" s="350" t="inlineStr">
+      <c r="F317" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="G317" s="350" t="inlineStr">
+      <c r="G317" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="H317" s="350" t="inlineStr">
+      <c r="H317" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -23750,27 +23751,27 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="J317" s="356" t="inlineStr">
+      <c r="J317" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="K317" s="350" t="inlineStr">
+      <c r="K317" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L317" s="350" t="inlineStr">
+      <c r="L317" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="M317" s="350" t="inlineStr">
+      <c r="M317" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="N317" s="350" t="inlineStr">
+      <c r="N317" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -23780,27 +23781,27 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="P317" s="356" t="inlineStr">
+      <c r="P317" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="Q317" s="350" t="inlineStr">
+      <c r="Q317" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R317" s="350" t="inlineStr">
+      <c r="R317" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="S317" s="350" t="inlineStr">
+      <c r="S317" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="T317" s="350" t="inlineStr">
+      <c r="T317" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -23825,79 +23826,79 @@
           <t>ノー部活ウィーク</t>
         </is>
       </c>
-      <c r="D318" s="356" t="inlineStr">
+      <c r="D318" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E318" s="350" t="inlineStr">
+      <c r="E318" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F318" s="350" t="inlineStr">
+      <c r="F318" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G318" s="350" t="inlineStr">
+      <c r="G318" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H318" s="350" t="inlineStr">
+      <c r="H318" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
       <c r="I318" s="180" t="n"/>
-      <c r="J318" s="356" t="inlineStr">
+      <c r="J318" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="K318" s="350" t="inlineStr">
+      <c r="K318" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L318" s="350" t="inlineStr">
+      <c r="L318" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="M318" s="350" t="inlineStr">
+      <c r="M318" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="N318" s="350" t="inlineStr">
+      <c r="N318" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
       <c r="O318" s="77" t="n"/>
-      <c r="P318" s="356" t="inlineStr">
+      <c r="P318" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="Q318" s="350" t="inlineStr">
+      <c r="Q318" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="R318" s="350" t="inlineStr">
+      <c r="R318" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="S318" s="350" t="inlineStr">
+      <c r="S318" s="349" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="T318" s="350" t="inlineStr">
+      <c r="T318" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -24013,92 +24014,92 @@
           <t>※【定時制１次入試】・ノー部活ウィーク・3年成績一覧表提出</t>
         </is>
       </c>
-      <c r="D322" s="356" t="inlineStr">
+      <c r="D322" s="358" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="E322" s="350" t="inlineStr">
+      <c r="E322" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="F322" s="350" t="inlineStr">
+      <c r="F322" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="G322" s="350" t="inlineStr">
+      <c r="G322" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="H322" s="350" t="inlineStr">
+      <c r="H322" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="I322" s="357" t="inlineStr">
+      <c r="I322" s="351" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="J322" s="356" t="inlineStr">
+      <c r="J322" s="358" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="K322" s="350" t="inlineStr">
+      <c r="K322" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="L322" s="350" t="inlineStr">
+      <c r="L322" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="M322" s="350" t="inlineStr">
+      <c r="M322" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="N322" s="350" t="inlineStr">
+      <c r="N322" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="O322" s="358" t="inlineStr">
+      <c r="O322" s="352" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="P322" s="356" t="inlineStr">
+      <c r="P322" s="358" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
       </c>
-      <c r="Q322" s="350" t="inlineStr">
+      <c r="Q322" s="349" t="inlineStr">
         <is>
           <t>金２</t>
         </is>
       </c>
-      <c r="R322" s="350" t="inlineStr">
+      <c r="R322" s="349" t="inlineStr">
         <is>
           <t>金３</t>
         </is>
       </c>
-      <c r="S322" s="350" t="inlineStr">
+      <c r="S322" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
       </c>
-      <c r="T322" s="350" t="inlineStr">
+      <c r="T322" s="349" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="U322" s="358" t="inlineStr">
+      <c r="U322" s="352" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -24144,7 +24145,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="I323" s="357" t="inlineStr">
+      <c r="I323" s="351" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -24174,7 +24175,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="O323" s="358" t="inlineStr">
+      <c r="O323" s="352" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -24204,7 +24205,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="U323" s="358" t="inlineStr">
+      <c r="U323" s="352" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -24229,9 +24230,9 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="E324" s="159" t="inlineStr">
-        <is>
-          <t>水２</t>
+      <c r="E324" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="F324" s="159" t="inlineStr">
@@ -24249,7 +24250,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="I324" s="357" t="inlineStr">
+      <c r="I324" s="351" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -24259,9 +24260,9 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="K324" s="159" t="inlineStr">
-        <is>
-          <t>水２</t>
+      <c r="K324" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="L324" s="159" t="inlineStr">
@@ -24279,7 +24280,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="O324" s="358" t="inlineStr">
+      <c r="O324" s="352" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -24289,9 +24290,9 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="Q324" s="159" t="inlineStr">
-        <is>
-          <t>水２</t>
+      <c r="Q324" s="349" t="inlineStr">
+        <is>
+          <t>火５</t>
         </is>
       </c>
       <c r="R324" s="159" t="inlineStr">
@@ -24309,7 +24310,7 @@
           <t>水５</t>
         </is>
       </c>
-      <c r="U324" s="358" t="inlineStr">
+      <c r="U324" s="352" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -24356,9 +24357,9 @@
           <t>木３</t>
         </is>
       </c>
-      <c r="S325" s="159" t="inlineStr">
-        <is>
-          <t>木４</t>
+      <c r="S325" s="349" t="inlineStr">
+        <is>
+          <t>金２</t>
         </is>
       </c>
       <c r="T325" s="159" t="inlineStr">
@@ -24489,7 +24490,7 @@
           <t>金１</t>
         </is>
       </c>
-      <c r="Q326" s="350" t="inlineStr">
+      <c r="Q326" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
@@ -24504,9 +24505,9 @@
           <t>金４</t>
         </is>
       </c>
-      <c r="T326" s="159" t="inlineStr">
-        <is>
-          <t>金５</t>
+      <c r="T326" s="349" t="inlineStr">
+        <is>
+          <t>月６</t>
         </is>
       </c>
       <c r="U326" s="77" t="inlineStr">
@@ -24843,89 +24844,89 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="E329" s="350" t="inlineStr">
+      <c r="E329" s="349" t="inlineStr">
+        <is>
+          <t>火６</t>
+        </is>
+      </c>
+      <c r="F329" s="159" t="inlineStr">
+        <is>
+          <t>月３</t>
+        </is>
+      </c>
+      <c r="G329" s="159" t="inlineStr">
+        <is>
+          <t>月４</t>
+        </is>
+      </c>
+      <c r="H329" s="159" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="I329" s="180" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="F329" s="159" t="inlineStr">
+      <c r="J329" s="158" t="inlineStr">
+        <is>
+          <t>月１</t>
+        </is>
+      </c>
+      <c r="K329" s="349" t="inlineStr">
+        <is>
+          <t>火６</t>
+        </is>
+      </c>
+      <c r="L329" s="159" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G329" s="159" t="inlineStr">
+      <c r="M329" s="159" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="H329" s="159" t="inlineStr">
+      <c r="N329" s="159" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
-      <c r="I329" s="357" t="inlineStr">
+      <c r="O329" s="77" t="inlineStr">
+        <is>
+          <t>月６</t>
+        </is>
+      </c>
+      <c r="P329" s="158" t="inlineStr">
+        <is>
+          <t>月１</t>
+        </is>
+      </c>
+      <c r="Q329" s="349" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
       </c>
-      <c r="J329" s="158" t="inlineStr">
-        <is>
-          <t>月１</t>
-        </is>
-      </c>
-      <c r="K329" s="350" t="inlineStr">
+      <c r="R329" s="159" t="inlineStr">
+        <is>
+          <t>月３</t>
+        </is>
+      </c>
+      <c r="S329" s="159" t="inlineStr">
+        <is>
+          <t>月４</t>
+        </is>
+      </c>
+      <c r="T329" s="159" t="inlineStr">
+        <is>
+          <t>月５</t>
+        </is>
+      </c>
+      <c r="U329" s="77" t="inlineStr">
         <is>
           <t>月６</t>
-        </is>
-      </c>
-      <c r="L329" s="159" t="inlineStr">
-        <is>
-          <t>月３</t>
-        </is>
-      </c>
-      <c r="M329" s="159" t="inlineStr">
-        <is>
-          <t>月４</t>
-        </is>
-      </c>
-      <c r="N329" s="159" t="inlineStr">
-        <is>
-          <t>月５</t>
-        </is>
-      </c>
-      <c r="O329" s="358" t="inlineStr">
-        <is>
-          <t>火６</t>
-        </is>
-      </c>
-      <c r="P329" s="158" t="inlineStr">
-        <is>
-          <t>月１</t>
-        </is>
-      </c>
-      <c r="Q329" s="350" t="inlineStr">
-        <is>
-          <t>月６</t>
-        </is>
-      </c>
-      <c r="R329" s="159" t="inlineStr">
-        <is>
-          <t>月３</t>
-        </is>
-      </c>
-      <c r="S329" s="159" t="inlineStr">
-        <is>
-          <t>月４</t>
-        </is>
-      </c>
-      <c r="T329" s="159" t="inlineStr">
-        <is>
-          <t>月５</t>
-        </is>
-      </c>
-      <c r="U329" s="358" t="inlineStr">
-        <is>
-          <t>火６</t>
         </is>
       </c>
       <c r="X329" s="44" t="inlineStr">
@@ -25048,9 +25049,9 @@
           <t>火３</t>
         </is>
       </c>
-      <c r="G330" s="159" t="inlineStr">
-        <is>
-          <t>火４</t>
+      <c r="G330" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
         </is>
       </c>
       <c r="H330" s="159" t="inlineStr">
@@ -25078,9 +25079,9 @@
           <t>火３</t>
         </is>
       </c>
-      <c r="M330" s="159" t="inlineStr">
-        <is>
-          <t>火４</t>
+      <c r="M330" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
         </is>
       </c>
       <c r="N330" s="159" t="inlineStr">
@@ -25108,9 +25109,9 @@
           <t>火３</t>
         </is>
       </c>
-      <c r="S330" s="159" t="inlineStr">
-        <is>
-          <t>火４</t>
+      <c r="S330" s="349" t="inlineStr">
+        <is>
+          <t>水５</t>
         </is>
       </c>
       <c r="T330" s="159" t="inlineStr">
@@ -25172,79 +25173,79 @@
 　　　　3年通知表(本)提出</t>
         </is>
       </c>
-      <c r="D332" s="356" t="inlineStr">
+      <c r="D332" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="E332" s="350" t="inlineStr">
+      <c r="E332" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="F332" s="350" t="inlineStr">
+      <c r="F332" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="G332" s="350" t="inlineStr">
+      <c r="G332" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="H332" s="350" t="inlineStr">
+      <c r="H332" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
       </c>
       <c r="I332" s="77" t="n"/>
-      <c r="J332" s="356" t="inlineStr">
+      <c r="J332" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="K332" s="350" t="inlineStr">
+      <c r="K332" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="L332" s="350" t="inlineStr">
+      <c r="L332" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="M332" s="350" t="inlineStr">
+      <c r="M332" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="N332" s="350" t="inlineStr">
+      <c r="N332" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
       </c>
       <c r="O332" s="77" t="n"/>
-      <c r="P332" s="356" t="inlineStr">
+      <c r="P332" s="358" t="inlineStr">
         <is>
           <t>水１</t>
         </is>
       </c>
-      <c r="Q332" s="350" t="inlineStr">
+      <c r="Q332" s="349" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="R332" s="350" t="inlineStr">
+      <c r="R332" s="349" t="inlineStr">
         <is>
           <t>水３</t>
         </is>
       </c>
-      <c r="S332" s="350" t="inlineStr">
+      <c r="S332" s="349" t="inlineStr">
         <is>
           <t>水４</t>
         </is>
       </c>
-      <c r="T332" s="350" t="inlineStr">
+      <c r="T332" s="349" t="inlineStr">
         <is>
           <t>水５</t>
         </is>
@@ -25265,7 +25266,7 @@
           <t>3送会リハ①・【公立一般Ｂ面接】</t>
         </is>
       </c>
-      <c r="D333" s="356" t="inlineStr">
+      <c r="D333" s="358" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -25295,7 +25296,7 @@
           <t>金６</t>
         </is>
       </c>
-      <c r="J333" s="356" t="inlineStr">
+      <c r="J333" s="358" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -25325,7 +25326,7 @@
           <t>金６</t>
         </is>
       </c>
-      <c r="P333" s="356" t="inlineStr">
+      <c r="P333" s="358" t="inlineStr">
         <is>
           <t>水６</t>
         </is>
@@ -25428,71 +25429,71 @@
           <t>3送会準備・リハ②</t>
         </is>
       </c>
-      <c r="D336" s="351" t="inlineStr">
+      <c r="D336" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="E336" s="352" t="inlineStr">
+      <c r="E336" s="354" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F336" s="352" t="inlineStr">
+      <c r="F336" s="354" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="G336" s="352" t="inlineStr">
+      <c r="G336" s="354" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="H336" s="353" t="n"/>
+      <c r="H336" s="355" t="n"/>
       <c r="I336" s="268" t="n"/>
-      <c r="J336" s="351" t="inlineStr">
+      <c r="J336" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="K336" s="352" t="inlineStr">
+      <c r="K336" s="354" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L336" s="352" t="inlineStr">
+      <c r="L336" s="354" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="M336" s="352" t="inlineStr">
+      <c r="M336" s="354" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="N336" s="353" t="n"/>
+      <c r="N336" s="355" t="n"/>
       <c r="O336" s="284" t="n"/>
-      <c r="P336" s="351" t="inlineStr">
+      <c r="P336" s="353" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="Q336" s="352" t="inlineStr">
+      <c r="Q336" s="354" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="R336" s="352" t="inlineStr">
+      <c r="R336" s="354" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="S336" s="352" t="inlineStr">
+      <c r="S336" s="354" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="T336" s="353" t="n"/>
+      <c r="T336" s="355" t="n"/>
       <c r="U336" s="284" t="n"/>
     </row>
     <row r="337" customFormat="1" s="47">
@@ -25509,7 +25510,7 @@
           <t>3年生を送る会</t>
         </is>
       </c>
-      <c r="D337" s="397" t="inlineStr">
+      <c r="D337" s="398" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
@@ -25531,7 +25532,7 @@
       </c>
       <c r="H337" s="262" t="n"/>
       <c r="I337" s="270" t="n"/>
-      <c r="J337" s="397" t="inlineStr">
+      <c r="J337" s="398" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
@@ -25553,7 +25554,7 @@
       </c>
       <c r="N337" s="262" t="n"/>
       <c r="O337" s="271" t="n"/>
-      <c r="P337" s="397" t="inlineStr">
+      <c r="P337" s="398" t="inlineStr">
         <is>
           <t>金１</t>
         </is>
@@ -25591,39 +25592,39 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="E338" s="159" t="inlineStr">
+      <c r="E338" s="349" t="inlineStr">
+        <is>
+          <t>水６</t>
+        </is>
+      </c>
+      <c r="F338" s="159" t="inlineStr">
+        <is>
+          <t>水３</t>
+        </is>
+      </c>
+      <c r="G338" s="159" t="inlineStr">
+        <is>
+          <t>水４</t>
+        </is>
+      </c>
+      <c r="H338" s="368" t="inlineStr">
+        <is>
+          <t>木５</t>
+        </is>
+      </c>
+      <c r="I338" s="351" t="inlineStr">
         <is>
           <t>水２</t>
         </is>
       </c>
-      <c r="F338" s="159" t="inlineStr">
-        <is>
-          <t>水３</t>
-        </is>
-      </c>
-      <c r="G338" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
-        </is>
-      </c>
-      <c r="H338" s="367" t="inlineStr">
-        <is>
-          <t>木５</t>
-        </is>
-      </c>
-      <c r="I338" s="180" t="inlineStr">
+      <c r="J338" s="158" t="inlineStr">
+        <is>
+          <t>水１</t>
+        </is>
+      </c>
+      <c r="K338" s="349" t="inlineStr">
         <is>
           <t>水６</t>
-        </is>
-      </c>
-      <c r="J338" s="158" t="inlineStr">
-        <is>
-          <t>水１</t>
-        </is>
-      </c>
-      <c r="K338" s="159" t="inlineStr">
-        <is>
-          <t>水２</t>
         </is>
       </c>
       <c r="L338" s="159" t="inlineStr">
@@ -25643,29 +25644,29 @@
           <t>水１</t>
         </is>
       </c>
-      <c r="Q338" s="159" t="inlineStr">
+      <c r="Q338" s="349" t="inlineStr">
+        <is>
+          <t>水６</t>
+        </is>
+      </c>
+      <c r="R338" s="159" t="inlineStr">
+        <is>
+          <t>水３</t>
+        </is>
+      </c>
+      <c r="S338" s="159" t="inlineStr">
+        <is>
+          <t>水４</t>
+        </is>
+      </c>
+      <c r="T338" s="368" t="inlineStr">
+        <is>
+          <t>木５</t>
+        </is>
+      </c>
+      <c r="U338" s="352" t="inlineStr">
         <is>
           <t>水２</t>
-        </is>
-      </c>
-      <c r="R338" s="159" t="inlineStr">
-        <is>
-          <t>水３</t>
-        </is>
-      </c>
-      <c r="S338" s="159" t="inlineStr">
-        <is>
-          <t>水４</t>
-        </is>
-      </c>
-      <c r="T338" s="367" t="inlineStr">
-        <is>
-          <t>木５</t>
-        </is>
-      </c>
-      <c r="U338" s="77" t="inlineStr">
-        <is>
-          <t>水６</t>
         </is>
       </c>
       <c r="X338" s="47" t="inlineStr">
@@ -25769,63 +25770,63 @@
         </is>
       </c>
       <c r="C339" s="41" t="n"/>
-      <c r="D339" s="386" t="inlineStr">
+      <c r="D339" s="387" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="E339" s="368" t="inlineStr">
+      <c r="E339" s="369" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F339" s="368" t="inlineStr">
+      <c r="F339" s="369" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="G339" s="368" t="inlineStr">
+      <c r="G339" s="369" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
       <c r="H339" s="190" t="n"/>
       <c r="I339" s="180" t="n"/>
-      <c r="J339" s="386" t="inlineStr">
+      <c r="J339" s="387" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
       <c r="K339" s="190" t="n"/>
       <c r="L339" s="190" t="n"/>
-      <c r="M339" s="368" t="inlineStr">
+      <c r="M339" s="369" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
       <c r="N339" s="190" t="n"/>
       <c r="O339" s="77" t="n"/>
-      <c r="P339" s="386" t="inlineStr">
+      <c r="P339" s="387" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
       </c>
-      <c r="Q339" s="368" t="inlineStr">
+      <c r="Q339" s="369" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="R339" s="368" t="inlineStr">
+      <c r="R339" s="369" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
       </c>
-      <c r="S339" s="368" t="inlineStr">
+      <c r="S339" s="369" t="inlineStr">
         <is>
           <t>月４</t>
         </is>
       </c>
-      <c r="T339" s="368" t="inlineStr">
+      <c r="T339" s="369" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -25951,47 +25952,47 @@
           <t>金３</t>
         </is>
       </c>
-      <c r="G340" s="368" t="inlineStr">
+      <c r="G340" s="369" t="inlineStr">
+        <is>
+          <t>金５</t>
+        </is>
+      </c>
+      <c r="H340" s="369" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="H340" s="190" t="inlineStr">
+      <c r="I340" s="180" t="inlineStr">
+        <is>
+          <t>金６</t>
+        </is>
+      </c>
+      <c r="J340" s="189" t="inlineStr">
+        <is>
+          <t>金１</t>
+        </is>
+      </c>
+      <c r="K340" s="190" t="inlineStr">
+        <is>
+          <t>金２</t>
+        </is>
+      </c>
+      <c r="L340" s="190" t="inlineStr">
+        <is>
+          <t>金３</t>
+        </is>
+      </c>
+      <c r="M340" s="369" t="inlineStr">
         <is>
           <t>金５</t>
         </is>
       </c>
-      <c r="I340" s="180" t="inlineStr">
-        <is>
-          <t>金６</t>
-        </is>
-      </c>
-      <c r="J340" s="189" t="inlineStr">
-        <is>
-          <t>金１</t>
-        </is>
-      </c>
-      <c r="K340" s="190" t="inlineStr">
-        <is>
-          <t>金２</t>
-        </is>
-      </c>
-      <c r="L340" s="190" t="inlineStr">
-        <is>
-          <t>金３</t>
-        </is>
-      </c>
-      <c r="M340" s="368" t="inlineStr">
+      <c r="N340" s="369" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
       </c>
-      <c r="N340" s="190" t="inlineStr">
-        <is>
-          <t>金５</t>
-        </is>
-      </c>
-      <c r="O340" s="349" t="inlineStr">
+      <c r="O340" s="350" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
@@ -25999,9 +26000,9 @@
       <c r="P340" s="189" t="n"/>
       <c r="Q340" s="190" t="n"/>
       <c r="R340" s="190" t="n"/>
-      <c r="S340" s="368" t="inlineStr">
-        <is>
-          <t>月６</t>
+      <c r="S340" s="369" t="inlineStr">
+        <is>
+          <t>金５</t>
         </is>
       </c>
       <c r="T340" s="190" t="n"/>
@@ -26334,27 +26335,27 @@
           <t>【公立一般合格発表】・卒業式準備</t>
         </is>
       </c>
-      <c r="D343" s="356" t="inlineStr">
+      <c r="D343" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="E343" s="350" t="inlineStr">
+      <c r="E343" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F343" s="350" t="inlineStr">
+      <c r="F343" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="G343" s="350" t="inlineStr">
+      <c r="G343" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="H343" s="350" t="inlineStr">
+      <c r="H343" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -26364,27 +26365,27 @@
           <t>月６</t>
         </is>
       </c>
-      <c r="J343" s="356" t="inlineStr">
+      <c r="J343" s="358" t="inlineStr">
         <is>
           <t>木１</t>
         </is>
       </c>
-      <c r="K343" s="350" t="inlineStr">
+      <c r="K343" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L343" s="350" t="inlineStr">
+      <c r="L343" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
       </c>
-      <c r="M343" s="350" t="inlineStr">
+      <c r="M343" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
       </c>
-      <c r="N343" s="350" t="inlineStr">
+      <c r="N343" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -26397,7 +26398,7 @@
       <c r="P343" s="158" t="n"/>
       <c r="Q343" s="159" t="n"/>
       <c r="R343" s="159" t="n"/>
-      <c r="S343" s="350" t="inlineStr">
+      <c r="S343" s="349" t="inlineStr">
         <is>
           <t>木４</t>
         </is>
@@ -26452,7 +26453,7 @@
           <t>選挙管理委員会・▼小中連絡会(汐路)・▼小中連絡会(陽明)</t>
         </is>
       </c>
-      <c r="D345" s="356" t="inlineStr">
+      <c r="D345" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -26482,7 +26483,7 @@
           <t>水６</t>
         </is>
       </c>
-      <c r="J345" s="356" t="inlineStr">
+      <c r="J345" s="358" t="inlineStr">
         <is>
           <t>火１</t>
         </is>
@@ -26538,12 +26539,12 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="E346" s="350" t="inlineStr">
+      <c r="E346" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F346" s="350" t="inlineStr">
+      <c r="F346" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -26553,7 +26554,7 @@
           <t>木４</t>
         </is>
       </c>
-      <c r="H346" s="350" t="inlineStr">
+      <c r="H346" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -26564,12 +26565,12 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="K346" s="350" t="inlineStr">
+      <c r="K346" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L346" s="350" t="inlineStr">
+      <c r="L346" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -26579,7 +26580,7 @@
           <t>木４</t>
         </is>
       </c>
-      <c r="N346" s="350" t="inlineStr">
+      <c r="N346" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
@@ -26734,12 +26735,12 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="E350" s="350" t="inlineStr">
+      <c r="E350" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="F350" s="350" t="inlineStr">
+      <c r="F350" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
@@ -26749,7 +26750,7 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="H350" s="350" t="inlineStr">
+      <c r="H350" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -26760,12 +26761,12 @@
           <t>月１</t>
         </is>
       </c>
-      <c r="K350" s="350" t="inlineStr">
+      <c r="K350" s="349" t="inlineStr">
         <is>
           <t>火２</t>
         </is>
       </c>
-      <c r="L350" s="350" t="inlineStr">
+      <c r="L350" s="349" t="inlineStr">
         <is>
           <t>火３</t>
         </is>
@@ -26775,7 +26776,7 @@
           <t>月４</t>
         </is>
       </c>
-      <c r="N350" s="350" t="inlineStr">
+      <c r="N350" s="349" t="inlineStr">
         <is>
           <t>火５</t>
         </is>
@@ -26807,12 +26808,12 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="E351" s="350" t="inlineStr">
+      <c r="E351" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="F351" s="350" t="inlineStr">
+      <c r="F351" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -26822,7 +26823,7 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="H351" s="350" t="inlineStr">
+      <c r="H351" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -26837,12 +26838,12 @@
           <t>火１</t>
         </is>
       </c>
-      <c r="K351" s="350" t="inlineStr">
+      <c r="K351" s="349" t="inlineStr">
         <is>
           <t>木２</t>
         </is>
       </c>
-      <c r="L351" s="350" t="inlineStr">
+      <c r="L351" s="349" t="inlineStr">
         <is>
           <t>木３</t>
         </is>
@@ -26852,7 +26853,7 @@
           <t>火４</t>
         </is>
       </c>
-      <c r="N351" s="350" t="inlineStr">
+      <c r="N351" s="349" t="inlineStr">
         <is>
           <t>木５</t>
         </is>
@@ -26893,12 +26894,12 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="F352" s="350" t="inlineStr">
+      <c r="F352" s="349" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="G352" s="350" t="inlineStr">
+      <c r="G352" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
@@ -26923,12 +26924,12 @@
           <t>水２</t>
         </is>
       </c>
-      <c r="L352" s="350" t="inlineStr">
+      <c r="L352" s="349" t="inlineStr">
         <is>
           <t>金６</t>
         </is>
       </c>
-      <c r="M352" s="350" t="inlineStr">
+      <c r="M352" s="349" t="inlineStr">
         <is>
           <t>金４</t>
         </is>
@@ -26969,12 +26970,12 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="E353" s="350" t="inlineStr">
+      <c r="E353" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="F353" s="350" t="inlineStr">
+      <c r="F353" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -26991,12 +26992,12 @@
           <t>木１</t>
         </is>
       </c>
-      <c r="K353" s="350" t="inlineStr">
+      <c r="K353" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
       </c>
-      <c r="L353" s="350" t="inlineStr">
+      <c r="L353" s="349" t="inlineStr">
         <is>
           <t>月３</t>
         </is>
@@ -27252,7 +27253,7 @@
           <t>火５</t>
         </is>
       </c>
-      <c r="O358" s="349" t="inlineStr">
+      <c r="O358" s="350" t="inlineStr">
         <is>
           <t>火６</t>
         </is>
@@ -27294,12 +27295,12 @@
           <t>水４</t>
         </is>
       </c>
-      <c r="H359" s="350" t="inlineStr">
+      <c r="H359" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
-      <c r="I359" s="357" t="inlineStr">
+      <c r="I359" s="351" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -27324,12 +27325,12 @@
           <t>水４</t>
         </is>
       </c>
-      <c r="N359" s="350" t="inlineStr">
+      <c r="N359" s="349" t="inlineStr">
         <is>
           <t>月５</t>
         </is>
       </c>
-      <c r="O359" s="358" t="inlineStr">
+      <c r="O359" s="352" t="inlineStr">
         <is>
           <t>月６</t>
         </is>
@@ -27355,7 +27356,7 @@
           <t>大掃除</t>
         </is>
       </c>
-      <c r="D360" s="356" t="inlineStr">
+      <c r="D360" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -27370,14 +27371,14 @@
           <t>木３</t>
         </is>
       </c>
-      <c r="G360" s="350" t="inlineStr">
-        <is>
-          <t>月４</t>
+      <c r="G360" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
         </is>
       </c>
       <c r="H360" s="159" t="n"/>
       <c r="I360" s="180" t="n"/>
-      <c r="J360" s="356" t="inlineStr">
+      <c r="J360" s="358" t="inlineStr">
         <is>
           <t>月１</t>
         </is>
@@ -27388,9 +27389,9 @@
         </is>
       </c>
       <c r="L360" s="159" t="n"/>
-      <c r="M360" s="350" t="inlineStr">
-        <is>
-          <t>月４</t>
+      <c r="M360" s="349" t="inlineStr">
+        <is>
+          <t>月５</t>
         </is>
       </c>
       <c r="N360" s="159" t="inlineStr">
@@ -27421,7 +27422,7 @@
         </is>
       </c>
       <c r="D361" s="158" t="n"/>
-      <c r="E361" s="350" t="inlineStr">
+      <c r="E361" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
@@ -27431,7 +27432,7 @@
       <c r="H361" s="159" t="n"/>
       <c r="I361" s="180" t="n"/>
       <c r="J361" s="158" t="n"/>
-      <c r="K361" s="350" t="inlineStr">
+      <c r="K361" s="349" t="inlineStr">
         <is>
           <t>月２</t>
         </is>
@@ -27549,22 +27550,22 @@
       </c>
       <c r="C365" s="41" t="n"/>
       <c r="D365" s="381" t="n"/>
-      <c r="E365" s="353" t="n"/>
-      <c r="F365" s="353" t="n"/>
-      <c r="G365" s="353" t="n"/>
-      <c r="H365" s="353" t="n"/>
+      <c r="E365" s="355" t="n"/>
+      <c r="F365" s="355" t="n"/>
+      <c r="G365" s="355" t="n"/>
+      <c r="H365" s="355" t="n"/>
       <c r="I365" s="268" t="n"/>
       <c r="J365" s="381" t="n"/>
-      <c r="K365" s="353" t="n"/>
-      <c r="L365" s="353" t="n"/>
-      <c r="M365" s="353" t="n"/>
-      <c r="N365" s="353" t="n"/>
+      <c r="K365" s="355" t="n"/>
+      <c r="L365" s="355" t="n"/>
+      <c r="M365" s="355" t="n"/>
+      <c r="N365" s="355" t="n"/>
       <c r="O365" s="284" t="n"/>
       <c r="P365" s="381" t="n"/>
-      <c r="Q365" s="353" t="n"/>
-      <c r="R365" s="353" t="n"/>
-      <c r="S365" s="353" t="n"/>
-      <c r="T365" s="353" t="n"/>
+      <c r="Q365" s="355" t="n"/>
+      <c r="R365" s="355" t="n"/>
+      <c r="S365" s="355" t="n"/>
+      <c r="T365" s="355" t="n"/>
       <c r="U365" s="284" t="n"/>
     </row>
     <row r="366" customFormat="1" s="47">
@@ -27606,24 +27607,24 @@
         </is>
       </c>
       <c r="C367" s="41" t="n"/>
-      <c r="D367" s="398" t="n"/>
-      <c r="E367" s="361" t="n"/>
-      <c r="F367" s="361" t="n"/>
-      <c r="G367" s="361" t="n"/>
-      <c r="H367" s="361" t="n"/>
-      <c r="I367" s="361" t="n"/>
-      <c r="J367" s="360" t="n"/>
-      <c r="K367" s="361" t="n"/>
-      <c r="L367" s="361" t="n"/>
-      <c r="M367" s="361" t="n"/>
-      <c r="N367" s="361" t="n"/>
-      <c r="O367" s="364" t="n"/>
-      <c r="P367" s="360" t="n"/>
-      <c r="Q367" s="361" t="n"/>
-      <c r="R367" s="361" t="n"/>
-      <c r="S367" s="361" t="n"/>
-      <c r="T367" s="361" t="n"/>
-      <c r="U367" s="364" t="n"/>
+      <c r="D367" s="399" t="n"/>
+      <c r="E367" s="362" t="n"/>
+      <c r="F367" s="362" t="n"/>
+      <c r="G367" s="362" t="n"/>
+      <c r="H367" s="362" t="n"/>
+      <c r="I367" s="362" t="n"/>
+      <c r="J367" s="361" t="n"/>
+      <c r="K367" s="362" t="n"/>
+      <c r="L367" s="362" t="n"/>
+      <c r="M367" s="362" t="n"/>
+      <c r="N367" s="362" t="n"/>
+      <c r="O367" s="365" t="n"/>
+      <c r="P367" s="361" t="n"/>
+      <c r="Q367" s="362" t="n"/>
+      <c r="R367" s="362" t="n"/>
+      <c r="S367" s="362" t="n"/>
+      <c r="T367" s="362" t="n"/>
+      <c r="U367" s="365" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="187" t="n">
@@ -27635,7 +27636,7 @@
         </is>
       </c>
       <c r="C368" s="41" t="n"/>
-      <c r="D368" s="399" t="n"/>
+      <c r="D368" s="400" t="n"/>
       <c r="E368" s="341" t="n"/>
       <c r="F368" s="341" t="n"/>
       <c r="G368" s="341" t="n"/>
@@ -40510,13 +40511,13 @@
       <c r="A18" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="400" t="inlineStr">
+      <c r="B18" s="401" t="inlineStr">
         <is>
           <t>選挙管理委員会
 　　　▼小中連絡会(汐路)</t>
         </is>
       </c>
-      <c r="C18" s="401" t="n"/>
+      <c r="C18" s="402" t="n"/>
       <c r="E18" s="95">
         <f t="array" ref="E18">INDEX($A:$A,ROW(A16)*2+2)</f>
         <v/>
@@ -40540,12 +40541,12 @@
           <t>火</t>
         </is>
       </c>
-      <c r="B19" s="402" t="inlineStr">
+      <c r="B19" s="403" t="inlineStr">
         <is>
           <t>1･2年通知表（本）提出</t>
         </is>
       </c>
-      <c r="C19" s="403" t="n"/>
+      <c r="C19" s="404" t="n"/>
       <c r="E19" s="95">
         <f t="array" ref="E19">INDEX($A:$A,ROW(A17)*2+2)</f>
         <v/>
@@ -40916,12 +40917,12 @@
           <t>火</t>
         </is>
       </c>
-      <c r="B33" s="404" t="inlineStr">
+      <c r="B33" s="405" t="inlineStr">
         <is>
           <t>【全日制･定時制２次選抜】</t>
         </is>
       </c>
-      <c r="C33" s="403" t="n"/>
+      <c r="C33" s="404" t="n"/>
       <c r="E33" s="95" t="n"/>
       <c r="G33" s="0">
         <f t="array" ref="G33">INDEX($C:$C,ROW(B32)*2)&amp;INDEX($C:$C,ROW(B32)*2+1)</f>
@@ -40946,12 +40947,12 @@
           <t>水</t>
         </is>
       </c>
-      <c r="B35" s="404" t="inlineStr">
+      <c r="B35" s="405" t="inlineStr">
         <is>
           <t>【全日制･定時制２次合格発表】</t>
         </is>
       </c>
-      <c r="C35" s="403" t="n"/>
+      <c r="C35" s="404" t="n"/>
       <c r="E35" s="95" t="n"/>
     </row>
     <row r="36" ht="18.75" customHeight="1" s="337">
@@ -40998,8 +40999,8 @@
           <t>金</t>
         </is>
       </c>
-      <c r="B39" s="404" t="n"/>
-      <c r="C39" s="403" t="n"/>
+      <c r="B39" s="405" t="n"/>
+      <c r="C39" s="404" t="n"/>
       <c r="E39" s="95" t="n"/>
     </row>
     <row r="40" ht="18.75" customHeight="1" s="337">
